--- a/data/nzd0304/nzd0304.xlsx
+++ b/data/nzd0304/nzd0304.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K729"/>
+  <dimension ref="A1:K733"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28875,6 +28875,162 @@
         <v>358.79</v>
       </c>
       <c r="K729" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-01 22:00:54+00:00</t>
+        </is>
+      </c>
+      <c r="B730" t="n">
+        <v>358.91</v>
+      </c>
+      <c r="C730" t="n">
+        <v>368</v>
+      </c>
+      <c r="D730" t="n">
+        <v>364.8</v>
+      </c>
+      <c r="E730" t="n">
+        <v>358.94</v>
+      </c>
+      <c r="F730" t="n">
+        <v>349.53</v>
+      </c>
+      <c r="G730" t="n">
+        <v>340.62</v>
+      </c>
+      <c r="H730" t="n">
+        <v>346.22</v>
+      </c>
+      <c r="I730" t="n">
+        <v>351.9</v>
+      </c>
+      <c r="J730" t="n">
+        <v>357.62</v>
+      </c>
+      <c r="K730" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-09 22:00:57+00:00</t>
+        </is>
+      </c>
+      <c r="B731" t="n">
+        <v>359.56</v>
+      </c>
+      <c r="C731" t="n">
+        <v>368.73</v>
+      </c>
+      <c r="D731" t="n">
+        <v>365.43</v>
+      </c>
+      <c r="E731" t="n">
+        <v>359.85</v>
+      </c>
+      <c r="F731" t="n">
+        <v>351.99</v>
+      </c>
+      <c r="G731" t="n">
+        <v>342.44</v>
+      </c>
+      <c r="H731" t="n">
+        <v>347.05</v>
+      </c>
+      <c r="I731" t="n">
+        <v>352.41</v>
+      </c>
+      <c r="J731" t="n">
+        <v>358.12</v>
+      </c>
+      <c r="K731" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-17 22:00:54+00:00</t>
+        </is>
+      </c>
+      <c r="B732" t="n">
+        <v>358.77</v>
+      </c>
+      <c r="C732" t="n">
+        <v>367.79</v>
+      </c>
+      <c r="D732" t="n">
+        <v>364.01</v>
+      </c>
+      <c r="E732" t="n">
+        <v>360.4</v>
+      </c>
+      <c r="F732" t="n">
+        <v>353.72</v>
+      </c>
+      <c r="G732" t="n">
+        <v>344.15</v>
+      </c>
+      <c r="H732" t="n">
+        <v>347.97</v>
+      </c>
+      <c r="I732" t="n">
+        <v>353.33</v>
+      </c>
+      <c r="J732" t="n">
+        <v>357.46</v>
+      </c>
+      <c r="K732" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-18 21:54:51+00:00</t>
+        </is>
+      </c>
+      <c r="B733" t="n">
+        <v>358.7</v>
+      </c>
+      <c r="C733" t="n">
+        <v>367.44</v>
+      </c>
+      <c r="D733" t="n">
+        <v>363.79</v>
+      </c>
+      <c r="E733" t="n">
+        <v>361.08</v>
+      </c>
+      <c r="F733" t="n">
+        <v>354.34</v>
+      </c>
+      <c r="G733" t="n">
+        <v>344.36</v>
+      </c>
+      <c r="H733" t="n">
+        <v>347.91</v>
+      </c>
+      <c r="I733" t="n">
+        <v>352.92</v>
+      </c>
+      <c r="J733" t="n">
+        <v>357.32</v>
+      </c>
+      <c r="K733" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -28891,7 +29047,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B737"/>
+  <dimension ref="A1:B741"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36264,6 +36420,46 @@
       </c>
       <c r="B737" t="n">
         <v>-0.44</v>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" t="inlineStr">
+        <is>
+          <t>2025-12-01 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B738" t="n">
+        <v>-0.39</v>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" t="inlineStr">
+        <is>
+          <t>2025-12-09 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B739" t="n">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" t="inlineStr">
+        <is>
+          <t>2025-12-17 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B740" t="n">
+        <v>-0.46</v>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" t="inlineStr">
+        <is>
+          <t>2025-12-18 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B741" t="n">
+        <v>-0.38</v>
       </c>
     </row>
   </sheetData>
@@ -36432,28 +36628,28 @@
         <v>0.0428</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.7395479822057127</v>
+        <v>-0.7380301616574736</v>
       </c>
       <c r="J2" t="n">
-        <v>728</v>
+        <v>732</v>
       </c>
       <c r="K2" t="n">
-        <v>728</v>
+        <v>732</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5289816271338376</v>
+        <v>0.5310257183418232</v>
       </c>
       <c r="M2" t="n">
-        <v>4.190299506194816</v>
+        <v>4.175839130136668</v>
       </c>
       <c r="N2" t="n">
-        <v>25.80671262344135</v>
+        <v>25.67591491117046</v>
       </c>
       <c r="O2" t="n">
-        <v>5.080030769930567</v>
+        <v>5.067140703707611</v>
       </c>
       <c r="P2" t="n">
-        <v>377.1344633881458</v>
+        <v>377.1185935023532</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -36510,28 +36706,28 @@
         <v>0.0458</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.6327057323701328</v>
+        <v>-0.6325043218098698</v>
       </c>
       <c r="J3" t="n">
-        <v>728</v>
+        <v>732</v>
       </c>
       <c r="K3" t="n">
-        <v>728</v>
+        <v>732</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4115997391993169</v>
+        <v>0.4145165760772364</v>
       </c>
       <c r="M3" t="n">
-        <v>4.387453344828462</v>
+        <v>4.365668635302002</v>
       </c>
       <c r="N3" t="n">
-        <v>30.32522397280368</v>
+        <v>30.16087458305742</v>
       </c>
       <c r="O3" t="n">
-        <v>5.506834296835495</v>
+        <v>5.491891712612096</v>
       </c>
       <c r="P3" t="n">
-        <v>384.4835218117854</v>
+        <v>384.4814178957284</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -36588,28 +36784,28 @@
         <v>0.0356</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.8014601800253701</v>
+        <v>-0.8014446227467524</v>
       </c>
       <c r="J4" t="n">
-        <v>728</v>
+        <v>732</v>
       </c>
       <c r="K4" t="n">
-        <v>728</v>
+        <v>732</v>
       </c>
       <c r="L4" t="n">
-        <v>0.389353329187939</v>
+        <v>0.3923608006567532</v>
       </c>
       <c r="M4" t="n">
-        <v>5.72632254521078</v>
+        <v>5.698281939675105</v>
       </c>
       <c r="N4" t="n">
-        <v>53.3841968732749</v>
+        <v>53.09473332218586</v>
       </c>
       <c r="O4" t="n">
-        <v>7.306448992039492</v>
+        <v>7.286613295776431</v>
       </c>
       <c r="P4" t="n">
-        <v>385.6107511977337</v>
+        <v>385.6105926941542</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -36666,28 +36862,28 @@
         <v>0.0368</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5703380454460901</v>
+        <v>-0.5706547512839291</v>
       </c>
       <c r="J5" t="n">
-        <v>728</v>
+        <v>732</v>
       </c>
       <c r="K5" t="n">
-        <v>728</v>
+        <v>732</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2762359393281686</v>
+        <v>0.278990861480609</v>
       </c>
       <c r="M5" t="n">
-        <v>5.359540205601417</v>
+        <v>5.333852538563804</v>
       </c>
       <c r="N5" t="n">
-        <v>45.16315067769028</v>
+        <v>44.92022271483697</v>
       </c>
       <c r="O5" t="n">
-        <v>6.720353463746553</v>
+        <v>6.70225504698508</v>
       </c>
       <c r="P5" t="n">
-        <v>375.3782473199824</v>
+        <v>375.3815518155403</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -36744,28 +36940,28 @@
         <v>0.0361</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4338732842525386</v>
+        <v>-0.4336048224752213</v>
       </c>
       <c r="J6" t="n">
-        <v>728</v>
+        <v>732</v>
       </c>
       <c r="K6" t="n">
-        <v>728</v>
+        <v>732</v>
       </c>
       <c r="L6" t="n">
-        <v>0.190844628677173</v>
+        <v>0.1925511379535461</v>
       </c>
       <c r="M6" t="n">
-        <v>5.326889172792364</v>
+        <v>5.306782817656521</v>
       </c>
       <c r="N6" t="n">
-        <v>42.29417050102214</v>
+        <v>42.08248516303491</v>
       </c>
       <c r="O6" t="n">
-        <v>6.503396843267534</v>
+        <v>6.487101445409568</v>
       </c>
       <c r="P6" t="n">
-        <v>363.5967994269519</v>
+        <v>363.5939749865198</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -36822,28 +37018,28 @@
         <v>0.0362</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3338864203197464</v>
+        <v>-0.3343722314293318</v>
       </c>
       <c r="J7" t="n">
-        <v>728</v>
+        <v>732</v>
       </c>
       <c r="K7" t="n">
-        <v>728</v>
+        <v>732</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1133358410814008</v>
+        <v>0.1148851683607182</v>
       </c>
       <c r="M7" t="n">
-        <v>5.529508632345931</v>
+        <v>5.50667071625673</v>
       </c>
       <c r="N7" t="n">
-        <v>46.21597362207449</v>
+        <v>45.97696445931403</v>
       </c>
       <c r="O7" t="n">
-        <v>6.798233125016712</v>
+        <v>6.780631567878764</v>
       </c>
       <c r="P7" t="n">
-        <v>352.1258092410931</v>
+        <v>352.1308750380421</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -36900,28 +37096,28 @@
         <v>0.036</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2514710559088573</v>
+        <v>-0.248158503503038</v>
       </c>
       <c r="J8" t="n">
-        <v>728</v>
+        <v>732</v>
       </c>
       <c r="K8" t="n">
-        <v>728</v>
+        <v>732</v>
       </c>
       <c r="L8" t="n">
-        <v>0.06149626529020591</v>
+        <v>0.06064978367433271</v>
       </c>
       <c r="M8" t="n">
-        <v>5.846610360359417</v>
+        <v>5.83169042490473</v>
       </c>
       <c r="N8" t="n">
-        <v>51.14061982620179</v>
+        <v>50.90973552823156</v>
       </c>
       <c r="O8" t="n">
-        <v>7.151267008453941</v>
+        <v>7.135105852629767</v>
       </c>
       <c r="P8" t="n">
-        <v>350.9935049407925</v>
+        <v>350.9588608150428</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -36978,28 +37174,28 @@
         <v>0.0354</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2244202378620422</v>
+        <v>-0.2179012535755627</v>
       </c>
       <c r="J9" t="n">
-        <v>728</v>
+        <v>732</v>
       </c>
       <c r="K9" t="n">
-        <v>728</v>
+        <v>732</v>
       </c>
       <c r="L9" t="n">
-        <v>0.04865294917072904</v>
+        <v>0.04640420037237636</v>
       </c>
       <c r="M9" t="n">
-        <v>5.888188978196205</v>
+        <v>5.888226757470544</v>
       </c>
       <c r="N9" t="n">
-        <v>52.18630583591365</v>
+        <v>52.07997029412646</v>
       </c>
       <c r="O9" t="n">
-        <v>7.224008986422542</v>
+        <v>7.216645362918041</v>
       </c>
       <c r="P9" t="n">
-        <v>352.8053442688602</v>
+        <v>352.737174232073</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -37056,28 +37252,28 @@
         <v>0.0406</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1372257493659228</v>
+        <v>-0.1320454085355509</v>
       </c>
       <c r="J10" t="n">
-        <v>728</v>
+        <v>732</v>
       </c>
       <c r="K10" t="n">
-        <v>728</v>
+        <v>732</v>
       </c>
       <c r="L10" t="n">
-        <v>0.02513935909986864</v>
+        <v>0.02354470788651031</v>
       </c>
       <c r="M10" t="n">
-        <v>4.953918332080204</v>
+        <v>4.951664644929673</v>
       </c>
       <c r="N10" t="n">
-        <v>38.69566103090457</v>
+        <v>38.59667565939775</v>
       </c>
       <c r="O10" t="n">
-        <v>6.220583656772456</v>
+        <v>6.212622285267128</v>
       </c>
       <c r="P10" t="n">
-        <v>356.6791628167193</v>
+        <v>356.6249962927042</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -37115,7 +37311,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K729"/>
+  <dimension ref="A1:K733"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -78671,6 +78867,234 @@
         </is>
       </c>
     </row>
+    <row r="730">
+      <c r="A730" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-01 22:00:54+00:00</t>
+        </is>
+      </c>
+      <c r="B730" t="inlineStr">
+        <is>
+          <t>-40.02177129953766,176.8912245186736</t>
+        </is>
+      </c>
+      <c r="C730" t="inlineStr">
+        <is>
+          <t>-40.022420297991864,176.89091671998423</t>
+        </is>
+      </c>
+      <c r="D730" t="inlineStr">
+        <is>
+          <t>-40.023022467329525,176.8904786219731</t>
+        </is>
+      </c>
+      <c r="E730" t="inlineStr">
+        <is>
+          <t>-40.02361449651713,176.89001232139202</t>
+        </is>
+      </c>
+      <c r="F730" t="inlineStr">
+        <is>
+          <t>-40.02419335864648,176.88950778207234</t>
+        </is>
+      </c>
+      <c r="G730" t="inlineStr">
+        <is>
+          <t>-40.024786031480645,176.88903246213656</t>
+        </is>
+      </c>
+      <c r="H730" t="inlineStr">
+        <is>
+          <t>-40.0254310647457,176.88871771725465</t>
+        </is>
+      </c>
+      <c r="I730" t="inlineStr">
+        <is>
+          <t>-40.02607614165642,176.88840402019784</t>
+        </is>
+      </c>
+      <c r="J730" t="inlineStr">
+        <is>
+          <t>-40.02672135355475,176.88809075519956</t>
+        </is>
+      </c>
+      <c r="K730" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-09 22:00:57+00:00</t>
+        </is>
+      </c>
+      <c r="B731" t="inlineStr">
+        <is>
+          <t>-40.02177377596411,176.8912314099802</t>
+        </is>
+      </c>
+      <c r="C731" t="inlineStr">
+        <is>
+          <t>-40.02242307921819,176.89092445952164</t>
+        </is>
+      </c>
+      <c r="D731" t="inlineStr">
+        <is>
+          <t>-40.0230248675817,176.8904853013516</t>
+        </is>
+      </c>
+      <c r="E731" t="inlineStr">
+        <is>
+          <t>-40.02361796357314,176.89002196945526</t>
+        </is>
+      </c>
+      <c r="F731" t="inlineStr">
+        <is>
+          <t>-40.024202415261826,176.88953405200877</t>
+        </is>
+      </c>
+      <c r="G731" t="inlineStr">
+        <is>
+          <t>-40.024792460885664,176.88905205206635</t>
+        </is>
+      </c>
+      <c r="H731" t="inlineStr">
+        <is>
+          <t>-40.02543398056872,176.88872666021416</t>
+        </is>
+      </c>
+      <c r="I731" t="inlineStr">
+        <is>
+          <t>-40.02607793331393,176.88840951531856</t>
+        </is>
+      </c>
+      <c r="J731" t="inlineStr">
+        <is>
+          <t>-40.026723110088675,176.88809614262115</t>
+        </is>
+      </c>
+      <c r="K731" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-17 22:00:54+00:00</t>
+        </is>
+      </c>
+      <c r="B732" t="inlineStr">
+        <is>
+          <t>-40.02177076615345,176.89122303439225</t>
+        </is>
+      </c>
+      <c r="C732" t="inlineStr">
+        <is>
+          <t>-40.02241949791294,176.89091449354206</t>
+        </is>
+      </c>
+      <c r="D732" t="inlineStr">
+        <is>
+          <t>-40.0230194574889,176.89047024624517</t>
+        </is>
+      </c>
+      <c r="E732" t="inlineStr">
+        <is>
+          <t>-40.023620059046145,176.8900278007027</t>
+        </is>
+      </c>
+      <c r="F732" t="inlineStr">
+        <is>
+          <t>-40.02420878434117,176.88955252639886</t>
+        </is>
+      </c>
+      <c r="G732" t="inlineStr">
+        <is>
+          <t>-40.02479850169707,176.88907045799255</t>
+        </is>
+      </c>
+      <c r="H732" t="inlineStr">
+        <is>
+          <t>-40.02543721256448,176.888736572893</t>
+        </is>
+      </c>
+      <c r="I732" t="inlineStr">
+        <is>
+          <t>-40.02608116532285,176.88841942808605</t>
+        </is>
+      </c>
+      <c r="J732" t="inlineStr">
+        <is>
+          <t>-40.02672079146383,176.8880890312247</t>
+        </is>
+      </c>
+      <c r="K732" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-18 21:54:51+00:00</t>
+        </is>
+      </c>
+      <c r="B733" t="inlineStr">
+        <is>
+          <t>-40.02177049946133,176.89122229225157</t>
+        </is>
+      </c>
+      <c r="C733" t="inlineStr">
+        <is>
+          <t>-40.022418164448,176.8909107828052</t>
+        </is>
+      </c>
+      <c r="D733" t="inlineStr">
+        <is>
+          <t>-40.02301861930532,176.8904679137641</t>
+        </is>
+      </c>
+      <c r="E733" t="inlineStr">
+        <is>
+          <t>-40.02362264981232,176.89003501024547</t>
+        </is>
+      </c>
+      <c r="F733" t="inlineStr">
+        <is>
+          <t>-40.02421106690064,176.88955914727936</t>
+        </is>
+      </c>
+      <c r="G733" t="inlineStr">
+        <is>
+          <t>-40.02479924355089,176.88907271836965</t>
+        </is>
+      </c>
+      <c r="H733" t="inlineStr">
+        <is>
+          <t>-40.025437001782194,176.88873592641391</t>
+        </is>
+      </c>
+      <c r="I733" t="inlineStr">
+        <is>
+          <t>-40.026079724971154,176.88841501043956</t>
+        </is>
+      </c>
+      <c r="J733" t="inlineStr">
+        <is>
+          <t>-40.02672029963426,176.8880875227467</t>
+        </is>
+      </c>
+      <c r="K733" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0304/nzd0304.xlsx
+++ b/data/nzd0304/nzd0304.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K733"/>
+  <dimension ref="A1:K734"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29031,6 +29031,45 @@
         <v>357.32</v>
       </c>
       <c r="K733" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-10 22:00:57+00:00</t>
+        </is>
+      </c>
+      <c r="B734" t="n">
+        <v>359.55</v>
+      </c>
+      <c r="C734" t="n">
+        <v>367.99</v>
+      </c>
+      <c r="D734" t="n">
+        <v>365.68</v>
+      </c>
+      <c r="E734" t="n">
+        <v>362.86</v>
+      </c>
+      <c r="F734" t="n">
+        <v>356.62</v>
+      </c>
+      <c r="G734" t="n">
+        <v>346.12</v>
+      </c>
+      <c r="H734" t="n">
+        <v>350.1</v>
+      </c>
+      <c r="I734" t="n">
+        <v>353.98</v>
+      </c>
+      <c r="J734" t="n">
+        <v>357.89</v>
+      </c>
+      <c r="K734" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -29047,7 +29086,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B741"/>
+  <dimension ref="A1:B742"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36460,6 +36499,16 @@
       </c>
       <c r="B741" t="n">
         <v>-0.38</v>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" t="inlineStr">
+        <is>
+          <t>2026-01-10 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B742" t="n">
+        <v>0.43</v>
       </c>
     </row>
   </sheetData>
@@ -36628,28 +36677,28 @@
         <v>0.0428</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.7380301616574736</v>
+        <v>-0.7374796356657232</v>
       </c>
       <c r="J2" t="n">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="K2" t="n">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5310257183418232</v>
+        <v>0.5313959817696264</v>
       </c>
       <c r="M2" t="n">
-        <v>4.175839130136668</v>
+        <v>4.173190078064125</v>
       </c>
       <c r="N2" t="n">
-        <v>25.67591491117046</v>
+        <v>25.64597809887868</v>
       </c>
       <c r="O2" t="n">
-        <v>5.067140703707611</v>
+        <v>5.064185827838338</v>
       </c>
       <c r="P2" t="n">
-        <v>377.1185935023532</v>
+        <v>377.1128176056734</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -36706,28 +36755,28 @@
         <v>0.0458</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.6325043218098698</v>
+        <v>-0.6324406334333087</v>
       </c>
       <c r="J3" t="n">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="K3" t="n">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4145165760772364</v>
+        <v>0.4152385716122989</v>
       </c>
       <c r="M3" t="n">
-        <v>4.365668635302002</v>
+        <v>4.36008035962189</v>
       </c>
       <c r="N3" t="n">
-        <v>30.16087458305742</v>
+        <v>30.11979555872179</v>
       </c>
       <c r="O3" t="n">
-        <v>5.491891712612096</v>
+        <v>5.488150467937426</v>
       </c>
       <c r="P3" t="n">
-        <v>384.4814178957284</v>
+        <v>384.4807497029669</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -36784,28 +36833,28 @@
         <v>0.0356</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.8014446227467524</v>
+        <v>-0.8010878714352125</v>
       </c>
       <c r="J4" t="n">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="K4" t="n">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3923608006567532</v>
+        <v>0.3928966573218733</v>
       </c>
       <c r="M4" t="n">
-        <v>5.698281939675105</v>
+        <v>5.692308146273017</v>
       </c>
       <c r="N4" t="n">
-        <v>53.09473332218586</v>
+        <v>53.02443664769212</v>
       </c>
       <c r="O4" t="n">
-        <v>7.286613295776431</v>
+        <v>7.281788011724326</v>
       </c>
       <c r="P4" t="n">
-        <v>385.6105926941542</v>
+        <v>385.6068498032704</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -36862,28 +36911,28 @@
         <v>0.0368</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5706547512839291</v>
+        <v>-0.5699269570718434</v>
       </c>
       <c r="J5" t="n">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="K5" t="n">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="L5" t="n">
-        <v>0.278990861480609</v>
+        <v>0.2790767887290651</v>
       </c>
       <c r="M5" t="n">
-        <v>5.333852538563804</v>
+        <v>5.330335096029719</v>
       </c>
       <c r="N5" t="n">
-        <v>44.92022271483697</v>
+        <v>44.86783870115163</v>
       </c>
       <c r="O5" t="n">
-        <v>6.70225504698508</v>
+        <v>6.698345967561815</v>
       </c>
       <c r="P5" t="n">
-        <v>375.3815518155403</v>
+        <v>375.3739160921846</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -36940,28 +36989,28 @@
         <v>0.0361</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4336048224752213</v>
+        <v>-0.4323276355103096</v>
       </c>
       <c r="J6" t="n">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="K6" t="n">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1925511379535461</v>
+        <v>0.1920271475388761</v>
       </c>
       <c r="M6" t="n">
-        <v>5.306782817656521</v>
+        <v>5.305829766885661</v>
       </c>
       <c r="N6" t="n">
-        <v>42.08248516303491</v>
+        <v>42.05247810853966</v>
       </c>
       <c r="O6" t="n">
-        <v>6.487101445409568</v>
+        <v>6.484788208456746</v>
       </c>
       <c r="P6" t="n">
-        <v>363.5939749865198</v>
+        <v>363.5805752559701</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -37018,28 +37067,28 @@
         <v>0.0362</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3343722314293318</v>
+        <v>-0.3335682025762078</v>
       </c>
       <c r="J7" t="n">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="K7" t="n">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1148851683607182</v>
+        <v>0.1146947811600331</v>
       </c>
       <c r="M7" t="n">
-        <v>5.50667071625673</v>
+        <v>5.503157120614526</v>
       </c>
       <c r="N7" t="n">
-        <v>45.97696445931403</v>
+        <v>45.92510064741781</v>
       </c>
       <c r="O7" t="n">
-        <v>6.780631567878764</v>
+        <v>6.776806080110144</v>
       </c>
       <c r="P7" t="n">
-        <v>352.1308750380421</v>
+        <v>352.1224394915778</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -37096,28 +37145,28 @@
         <v>0.036</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.248158503503038</v>
+        <v>-0.2465371373631865</v>
       </c>
       <c r="J8" t="n">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="K8" t="n">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="L8" t="n">
-        <v>0.06064978367433271</v>
+        <v>0.06003737478331683</v>
       </c>
       <c r="M8" t="n">
-        <v>5.83169042490473</v>
+        <v>5.832035141275814</v>
       </c>
       <c r="N8" t="n">
-        <v>50.90973552823156</v>
+        <v>50.88444587032505</v>
       </c>
       <c r="O8" t="n">
-        <v>7.135105852629767</v>
+        <v>7.133333433278235</v>
       </c>
       <c r="P8" t="n">
-        <v>350.9588608150428</v>
+        <v>350.9418500953962</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -37174,28 +37223,28 @@
         <v>0.0354</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2179012535755627</v>
+        <v>-0.2159097406546407</v>
       </c>
       <c r="J9" t="n">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="K9" t="n">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="L9" t="n">
-        <v>0.04640420037237636</v>
+        <v>0.04568100283808785</v>
       </c>
       <c r="M9" t="n">
-        <v>5.888226757470544</v>
+        <v>5.889994754715937</v>
       </c>
       <c r="N9" t="n">
-        <v>52.07997029412646</v>
+        <v>52.07555068368519</v>
       </c>
       <c r="O9" t="n">
-        <v>7.216645362918041</v>
+        <v>7.216339146941833</v>
       </c>
       <c r="P9" t="n">
-        <v>352.737174232073</v>
+        <v>352.7162800816786</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -37252,28 +37301,28 @@
         <v>0.0406</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1320454085355509</v>
+        <v>-0.1306919085129723</v>
       </c>
       <c r="J10" t="n">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="K10" t="n">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="L10" t="n">
-        <v>0.02354470788651031</v>
+        <v>0.02312928996584529</v>
       </c>
       <c r="M10" t="n">
-        <v>4.951664644929673</v>
+        <v>4.951362544995939</v>
       </c>
       <c r="N10" t="n">
-        <v>38.59667565939775</v>
+        <v>38.57479683737947</v>
       </c>
       <c r="O10" t="n">
-        <v>6.212622285267128</v>
+        <v>6.210861199332945</v>
       </c>
       <c r="P10" t="n">
-        <v>356.6249962927042</v>
+        <v>356.6107959163302</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -37311,7 +37360,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K733"/>
+  <dimension ref="A1:K734"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -79095,6 +79144,63 @@
         </is>
       </c>
     </row>
+    <row r="734">
+      <c r="A734" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-10 22:00:57+00:00</t>
+        </is>
+      </c>
+      <c r="B734" t="inlineStr">
+        <is>
+          <t>-40.02177373786525,176.8912313039601</t>
+        </is>
+      </c>
+      <c r="C734" t="inlineStr">
+        <is>
+          <t>-40.02242025989287,176.89091661396316</t>
+        </is>
+      </c>
+      <c r="D734" t="inlineStr">
+        <is>
+          <t>-40.02302582006261,176.89048795189873</t>
+        </is>
+      </c>
+      <c r="E734" t="inlineStr">
+        <is>
+          <t>-40.02362943152153,176.89005388228637</t>
+        </is>
+      </c>
+      <c r="F734" t="inlineStr">
+        <is>
+          <t>-40.02421946082557,176.889583495037</t>
+        </is>
+      </c>
+      <c r="G734" t="inlineStr">
+        <is>
+          <t>-40.0248054609906,176.88909166248442</t>
+        </is>
+      </c>
+      <c r="H734" t="inlineStr">
+        <is>
+          <t>-40.02544469533383,176.8887595229029</t>
+        </is>
+      </c>
+      <c r="I734" t="inlineStr">
+        <is>
+          <t>-40.026083448806865,176.8884264316723</t>
+        </is>
+      </c>
+      <c r="J734" t="inlineStr">
+        <is>
+          <t>-40.0267223020831,176.88809366440717</t>
+        </is>
+      </c>
+      <c r="K734" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0304/nzd0304.xlsx
+++ b/data/nzd0304/nzd0304.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K734"/>
+  <dimension ref="A1:K736"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29070,6 +29070,84 @@
         <v>357.89</v>
       </c>
       <c r="K734" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-04 21:54:43+00:00</t>
+        </is>
+      </c>
+      <c r="B735" t="n">
+        <v>362.37</v>
+      </c>
+      <c r="C735" t="n">
+        <v>370.26</v>
+      </c>
+      <c r="D735" t="n">
+        <v>368.33</v>
+      </c>
+      <c r="E735" t="n">
+        <v>365.45</v>
+      </c>
+      <c r="F735" t="n">
+        <v>358.85</v>
+      </c>
+      <c r="G735" t="n">
+        <v>348.53</v>
+      </c>
+      <c r="H735" t="n">
+        <v>351.44</v>
+      </c>
+      <c r="I735" t="n">
+        <v>354.61</v>
+      </c>
+      <c r="J735" t="n">
+        <v>358</v>
+      </c>
+      <c r="K735" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-20 21:54:36+00:00</t>
+        </is>
+      </c>
+      <c r="B736" t="n">
+        <v>361.82</v>
+      </c>
+      <c r="C736" t="n">
+        <v>370.45</v>
+      </c>
+      <c r="D736" t="n">
+        <v>368.28</v>
+      </c>
+      <c r="E736" t="n">
+        <v>365.7</v>
+      </c>
+      <c r="F736" t="n">
+        <v>359.64</v>
+      </c>
+      <c r="G736" t="n">
+        <v>349.25</v>
+      </c>
+      <c r="H736" t="n">
+        <v>351.27</v>
+      </c>
+      <c r="I736" t="n">
+        <v>353.31</v>
+      </c>
+      <c r="J736" t="n">
+        <v>357.42</v>
+      </c>
+      <c r="K736" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -29086,7 +29164,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B742"/>
+  <dimension ref="A1:B744"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36509,6 +36587,26 @@
       </c>
       <c r="B742" t="n">
         <v>0.43</v>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" t="inlineStr">
+        <is>
+          <t>2026-02-04 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B743" t="n">
+        <v>0.48</v>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" t="inlineStr">
+        <is>
+          <t>2026-02-20 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B744" t="n">
+        <v>0.51</v>
       </c>
     </row>
   </sheetData>
@@ -36677,28 +36775,28 @@
         <v>0.0428</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.7374796356657232</v>
+        <v>-0.7348985166127525</v>
       </c>
       <c r="J2" t="n">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="K2" t="n">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5313959817696264</v>
+        <v>0.5307006365243977</v>
       </c>
       <c r="M2" t="n">
-        <v>4.173190078064125</v>
+        <v>4.176017904374949</v>
       </c>
       <c r="N2" t="n">
-        <v>25.64597809887868</v>
+        <v>25.63206392811036</v>
       </c>
       <c r="O2" t="n">
-        <v>5.064185827838338</v>
+        <v>5.062811859837413</v>
       </c>
       <c r="P2" t="n">
-        <v>377.1128176056734</v>
+        <v>377.0856393354762</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -36755,28 +36853,28 @@
         <v>0.0458</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.6324406334333087</v>
+        <v>-0.6309352951109658</v>
       </c>
       <c r="J3" t="n">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="K3" t="n">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4152385716122989</v>
+        <v>0.4154825826315096</v>
       </c>
       <c r="M3" t="n">
-        <v>4.36008035962189</v>
+        <v>4.35684769316232</v>
       </c>
       <c r="N3" t="n">
-        <v>30.11979555872179</v>
+        <v>30.05680124279915</v>
       </c>
       <c r="O3" t="n">
-        <v>5.488150467937426</v>
+        <v>5.48240834331037</v>
       </c>
       <c r="P3" t="n">
-        <v>384.4807497029669</v>
+        <v>384.464897639765</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -36833,28 +36931,28 @@
         <v>0.0356</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.8010878714352125</v>
+        <v>-0.7988461356807993</v>
       </c>
       <c r="J4" t="n">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="K4" t="n">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3928966573218733</v>
+        <v>0.3928975319420247</v>
       </c>
       <c r="M4" t="n">
-        <v>5.692308146273017</v>
+        <v>5.688030717823563</v>
       </c>
       <c r="N4" t="n">
-        <v>53.02443664769212</v>
+        <v>52.92214696337523</v>
       </c>
       <c r="O4" t="n">
-        <v>7.281788011724326</v>
+        <v>7.274760955754851</v>
       </c>
       <c r="P4" t="n">
-        <v>385.6068498032704</v>
+        <v>385.5832439494104</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -36911,28 +37009,28 @@
         <v>0.0368</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5699269570718434</v>
+        <v>-0.5669084136716337</v>
       </c>
       <c r="J5" t="n">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="K5" t="n">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2790767887290651</v>
+        <v>0.2778872909196128</v>
       </c>
       <c r="M5" t="n">
-        <v>5.330335096029719</v>
+        <v>5.331259575530438</v>
       </c>
       <c r="N5" t="n">
-        <v>44.86783870115163</v>
+        <v>44.82193362692713</v>
       </c>
       <c r="O5" t="n">
-        <v>6.698345967561815</v>
+        <v>6.694918492926343</v>
       </c>
       <c r="P5" t="n">
-        <v>375.3739160921846</v>
+        <v>375.3421295350265</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -36989,28 +37087,28 @@
         <v>0.0361</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4323276355103096</v>
+        <v>-0.4282757768978251</v>
       </c>
       <c r="J6" t="n">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="K6" t="n">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1920271475388761</v>
+        <v>0.1896020459778277</v>
       </c>
       <c r="M6" t="n">
-        <v>5.305829766885661</v>
+        <v>5.311209244163813</v>
       </c>
       <c r="N6" t="n">
-        <v>42.05247810853966</v>
+        <v>42.07564856229486</v>
       </c>
       <c r="O6" t="n">
-        <v>6.484788208456746</v>
+        <v>6.486574485989879</v>
       </c>
       <c r="P6" t="n">
-        <v>363.5805752559701</v>
+        <v>363.5379062991343</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -37067,28 +37165,28 @@
         <v>0.0362</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3335682025762078</v>
+        <v>-0.3303781148398687</v>
       </c>
       <c r="J7" t="n">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="K7" t="n">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1146947811600331</v>
+        <v>0.113212626536309</v>
       </c>
       <c r="M7" t="n">
-        <v>5.503157120614526</v>
+        <v>5.503954990925764</v>
       </c>
       <c r="N7" t="n">
-        <v>45.92510064741781</v>
+        <v>45.88551976308193</v>
       </c>
       <c r="O7" t="n">
-        <v>6.776806080110144</v>
+        <v>6.773885130638246</v>
       </c>
       <c r="P7" t="n">
-        <v>352.1224394915778</v>
+        <v>352.0888453217925</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -37145,28 +37243,28 @@
         <v>0.036</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2465371373631865</v>
+        <v>-0.2425855362179158</v>
       </c>
       <c r="J8" t="n">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="K8" t="n">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="L8" t="n">
-        <v>0.06003737478331683</v>
+        <v>0.05844999715098742</v>
       </c>
       <c r="M8" t="n">
-        <v>5.832035141275814</v>
+        <v>5.836194781113905</v>
       </c>
       <c r="N8" t="n">
-        <v>50.88444587032505</v>
+        <v>50.87649457001864</v>
       </c>
       <c r="O8" t="n">
-        <v>7.133333433278235</v>
+        <v>7.132776077378193</v>
       </c>
       <c r="P8" t="n">
-        <v>350.9418500953962</v>
+        <v>350.9002394290703</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -37223,28 +37321,28 @@
         <v>0.0354</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2159097406546407</v>
+        <v>-0.2119525080984624</v>
       </c>
       <c r="J9" t="n">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="K9" t="n">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="L9" t="n">
-        <v>0.04568100283808785</v>
+        <v>0.04425811818570025</v>
       </c>
       <c r="M9" t="n">
-        <v>5.889994754715937</v>
+        <v>5.893381332309779</v>
       </c>
       <c r="N9" t="n">
-        <v>52.07555068368519</v>
+        <v>52.06588719728877</v>
       </c>
       <c r="O9" t="n">
-        <v>7.216339146941833</v>
+        <v>7.215669559873759</v>
       </c>
       <c r="P9" t="n">
-        <v>352.7162800816786</v>
+        <v>352.6746131203238</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -37301,28 +37399,28 @@
         <v>0.0406</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1306919085129723</v>
+        <v>-0.128098477585563</v>
       </c>
       <c r="J10" t="n">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="K10" t="n">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="L10" t="n">
-        <v>0.02312928996584529</v>
+        <v>0.02234825483150649</v>
       </c>
       <c r="M10" t="n">
-        <v>4.951362544995939</v>
+        <v>4.950206564526232</v>
       </c>
       <c r="N10" t="n">
-        <v>38.57479683737947</v>
+        <v>38.52627151406358</v>
       </c>
       <c r="O10" t="n">
-        <v>6.210861199332945</v>
+        <v>6.20695348090056</v>
       </c>
       <c r="P10" t="n">
-        <v>356.6107959163302</v>
+        <v>356.5834881273321</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -37360,7 +37458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K734"/>
+  <dimension ref="A1:K736"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -79201,6 +79299,120 @@
         </is>
       </c>
     </row>
+    <row r="735">
+      <c r="A735" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-04 21:54:43+00:00</t>
+        </is>
+      </c>
+      <c r="B735" t="inlineStr">
+        <is>
+          <t>-40.02178448174114,176.89126120163428</t>
+        </is>
+      </c>
+      <c r="C735" t="inlineStr">
+        <is>
+          <t>-40.02242890836202,176.89094068074587</t>
+        </is>
+      </c>
+      <c r="D735" t="inlineStr">
+        <is>
+          <t>-40.0230359163563,176.8905160477027</t>
+        </is>
+      </c>
+      <c r="E735" t="inlineStr">
+        <is>
+          <t>-40.023639299283595,176.89008134217244</t>
+        </is>
+      </c>
+      <c r="F735" t="inlineStr">
+        <is>
+          <t>-40.02422767066796,176.88960730885805</t>
+        </is>
+      </c>
+      <c r="G735" t="inlineStr">
+        <is>
+          <t>-40.02481397463851,176.88911760301045</t>
+        </is>
+      </c>
+      <c r="H735" t="inlineStr">
+        <is>
+          <t>-40.02544940280129,176.8887739609397</t>
+        </is>
+      </c>
+      <c r="I735" t="inlineStr">
+        <is>
+          <t>-40.02608566202943,176.888433219764</t>
+        </is>
+      </c>
+      <c r="J735" t="inlineStr">
+        <is>
+          <t>-40.026722688520564,176.88809484963994</t>
+        </is>
+      </c>
+      <c r="K735" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-20 21:54:36+00:00</t>
+        </is>
+      </c>
+      <c r="B736" t="inlineStr">
+        <is>
+          <t>-40.02178238630499,176.89125537052692</t>
+        </is>
+      </c>
+      <c r="C736" t="inlineStr">
+        <is>
+          <t>-40.022429632242456,176.89094269514644</t>
+        </is>
+      </c>
+      <c r="D736" t="inlineStr">
+        <is>
+          <t>-40.02303572586026,176.89051551759312</t>
+        </is>
+      </c>
+      <c r="E736" t="inlineStr">
+        <is>
+          <t>-40.02364025176991,176.890083992741</t>
+        </is>
+      </c>
+      <c r="F736" t="inlineStr">
+        <is>
+          <t>-40.024230579086215,176.88961574514573</t>
+        </is>
+      </c>
+      <c r="G736" t="inlineStr">
+        <is>
+          <t>-40.02481651813379,176.88912535287832</t>
+        </is>
+      </c>
+      <c r="H736" t="inlineStr">
+        <is>
+          <t>-40.02544880558537,176.88877212924834</t>
+        </is>
+      </c>
+      <c r="I736" t="inlineStr">
+        <is>
+          <t>-40.02608109506178,176.8884192125911</t>
+        </is>
+      </c>
+      <c r="J736" t="inlineStr">
+        <is>
+          <t>-40.0267206509411,176.888088600231</t>
+        </is>
+      </c>
+      <c r="K736" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0304/nzd0304.xlsx
+++ b/data/nzd0304/nzd0304.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K736"/>
+  <dimension ref="A1:K738"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29148,6 +29148,84 @@
         <v>357.42</v>
       </c>
       <c r="K736" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-28 21:54:27+00:00</t>
+        </is>
+      </c>
+      <c r="B737" t="n">
+        <v>362.17</v>
+      </c>
+      <c r="C737" t="n">
+        <v>371.25</v>
+      </c>
+      <c r="D737" t="n">
+        <v>369.74</v>
+      </c>
+      <c r="E737" t="n">
+        <v>368.72</v>
+      </c>
+      <c r="F737" t="n">
+        <v>362.23</v>
+      </c>
+      <c r="G737" t="n">
+        <v>352.13</v>
+      </c>
+      <c r="H737" t="n">
+        <v>354.22</v>
+      </c>
+      <c r="I737" t="n">
+        <v>355.42</v>
+      </c>
+      <c r="J737" t="n">
+        <v>359.17</v>
+      </c>
+      <c r="K737" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-15 22:00:37+00:00</t>
+        </is>
+      </c>
+      <c r="B738" t="n">
+        <v>361.38</v>
+      </c>
+      <c r="C738" t="n">
+        <v>370.52</v>
+      </c>
+      <c r="D738" t="n">
+        <v>369.49</v>
+      </c>
+      <c r="E738" t="n">
+        <v>368.37</v>
+      </c>
+      <c r="F738" t="n">
+        <v>361.91</v>
+      </c>
+      <c r="G738" t="n">
+        <v>351.31</v>
+      </c>
+      <c r="H738" t="n">
+        <v>353.11</v>
+      </c>
+      <c r="I738" t="n">
+        <v>353.97</v>
+      </c>
+      <c r="J738" t="n">
+        <v>358.19</v>
+      </c>
+      <c r="K738" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -29164,7 +29242,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B744"/>
+  <dimension ref="A1:B746"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36607,6 +36685,26 @@
       </c>
       <c r="B744" t="n">
         <v>0.51</v>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" t="inlineStr">
+        <is>
+          <t>2026-02-28 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B745" t="n">
+        <v>-0.64</v>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" t="inlineStr">
+        <is>
+          <t>2026-03-15 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B746" t="n">
+        <v>-0.47</v>
       </c>
     </row>
   </sheetData>
@@ -36775,28 +36873,28 @@
         <v>0.0428</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.7348985166127525</v>
+        <v>-0.7325042989513069</v>
       </c>
       <c r="J2" t="n">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="K2" t="n">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5307006365243977</v>
+        <v>0.5301968171016744</v>
       </c>
       <c r="M2" t="n">
-        <v>4.176017904374949</v>
+        <v>4.177763962536942</v>
       </c>
       <c r="N2" t="n">
-        <v>25.63206392811036</v>
+        <v>25.61101683925185</v>
       </c>
       <c r="O2" t="n">
-        <v>5.062811859837413</v>
+        <v>5.060732836186064</v>
       </c>
       <c r="P2" t="n">
-        <v>377.0856393354762</v>
+        <v>377.0603641920784</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -36853,28 +36951,28 @@
         <v>0.0458</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.6309352951109658</v>
+        <v>-0.6291267685657033</v>
       </c>
       <c r="J3" t="n">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="K3" t="n">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4154825826315096</v>
+        <v>0.4154174967140333</v>
       </c>
       <c r="M3" t="n">
-        <v>4.35684769316232</v>
+        <v>4.355354194912446</v>
       </c>
       <c r="N3" t="n">
-        <v>30.05680124279915</v>
+        <v>30.00302088468148</v>
       </c>
       <c r="O3" t="n">
-        <v>5.48240834331037</v>
+        <v>5.477501335890433</v>
       </c>
       <c r="P3" t="n">
-        <v>384.464897639765</v>
+        <v>384.4458057836142</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -36931,28 +37029,28 @@
         <v>0.0356</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.7988461356807993</v>
+        <v>-0.7958617393908172</v>
       </c>
       <c r="J4" t="n">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="K4" t="n">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3928975319420247</v>
+        <v>0.3923009382233861</v>
       </c>
       <c r="M4" t="n">
-        <v>5.688030717823563</v>
+        <v>5.687489833903615</v>
       </c>
       <c r="N4" t="n">
-        <v>52.92214696337523</v>
+        <v>52.85329896270225</v>
       </c>
       <c r="O4" t="n">
-        <v>7.274760955754851</v>
+        <v>7.270027438923615</v>
       </c>
       <c r="P4" t="n">
-        <v>385.5832439494104</v>
+        <v>385.5517365995723</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -37009,28 +37107,28 @@
         <v>0.0368</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5669084136716337</v>
+        <v>-0.5622239839793493</v>
       </c>
       <c r="J5" t="n">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="K5" t="n">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2778872909196128</v>
+        <v>0.2750253480623746</v>
       </c>
       <c r="M5" t="n">
-        <v>5.331259575530438</v>
+        <v>5.340910246332232</v>
       </c>
       <c r="N5" t="n">
-        <v>44.82193362692713</v>
+        <v>44.88450739533625</v>
       </c>
       <c r="O5" t="n">
-        <v>6.694918492926343</v>
+        <v>6.699590091590399</v>
       </c>
       <c r="P5" t="n">
-        <v>375.3421295350265</v>
+        <v>375.2926743097134</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -37087,28 +37185,28 @@
         <v>0.0361</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4282757768978251</v>
+        <v>-0.4226618347118999</v>
       </c>
       <c r="J6" t="n">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="K6" t="n">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1896020459778277</v>
+        <v>0.1855978102417259</v>
       </c>
       <c r="M6" t="n">
-        <v>5.311209244163813</v>
+        <v>5.324439922851083</v>
       </c>
       <c r="N6" t="n">
-        <v>42.07564856229486</v>
+        <v>42.22598412391434</v>
       </c>
       <c r="O6" t="n">
-        <v>6.486574485989879</v>
+        <v>6.49815236231918</v>
       </c>
       <c r="P6" t="n">
-        <v>363.5379062991343</v>
+        <v>363.4786376525453</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -37165,28 +37263,28 @@
         <v>0.0362</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3303781148398687</v>
+        <v>-0.3256154313527374</v>
       </c>
       <c r="J7" t="n">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="K7" t="n">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="L7" t="n">
-        <v>0.113212626536309</v>
+        <v>0.1105495305298865</v>
       </c>
       <c r="M7" t="n">
-        <v>5.503954990925764</v>
+        <v>5.512498294997375</v>
       </c>
       <c r="N7" t="n">
-        <v>45.88551976308193</v>
+        <v>45.95179180393608</v>
       </c>
       <c r="O7" t="n">
-        <v>6.773885130638246</v>
+        <v>6.778775096131755</v>
       </c>
       <c r="P7" t="n">
-        <v>352.0888453217925</v>
+        <v>352.0385650989411</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -37243,28 +37341,28 @@
         <v>0.036</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2425855362179158</v>
+        <v>-0.2373694667079166</v>
       </c>
       <c r="J8" t="n">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="K8" t="n">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="L8" t="n">
-        <v>0.05844999715098742</v>
+        <v>0.05620329222507847</v>
       </c>
       <c r="M8" t="n">
-        <v>5.836194781113905</v>
+        <v>5.84689630976179</v>
       </c>
       <c r="N8" t="n">
-        <v>50.87649457001864</v>
+        <v>50.96758286268261</v>
       </c>
       <c r="O8" t="n">
-        <v>7.132776077378193</v>
+        <v>7.139158414174783</v>
       </c>
       <c r="P8" t="n">
-        <v>350.9002394290703</v>
+        <v>350.8451733032928</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -37321,28 +37419,28 @@
         <v>0.0354</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2119525080984624</v>
+        <v>-0.207617935689081</v>
       </c>
       <c r="J9" t="n">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="K9" t="n">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="L9" t="n">
-        <v>0.04425811818570025</v>
+        <v>0.04267890070838221</v>
       </c>
       <c r="M9" t="n">
-        <v>5.893381332309779</v>
+        <v>5.898485603652763</v>
       </c>
       <c r="N9" t="n">
-        <v>52.06588719728877</v>
+        <v>52.08369306146195</v>
       </c>
       <c r="O9" t="n">
-        <v>7.215669559873759</v>
+        <v>7.216903287523115</v>
       </c>
       <c r="P9" t="n">
-        <v>352.6746131203238</v>
+        <v>352.6288542688844</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -37399,28 +37497,28 @@
         <v>0.0406</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.128098477585563</v>
+        <v>-0.124981995640974</v>
       </c>
       <c r="J10" t="n">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="K10" t="n">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="L10" t="n">
-        <v>0.02234825483150649</v>
+        <v>0.02138599436122213</v>
       </c>
       <c r="M10" t="n">
-        <v>4.950206564526232</v>
+        <v>4.951564505699505</v>
       </c>
       <c r="N10" t="n">
-        <v>38.52627151406358</v>
+        <v>38.50388187886627</v>
       </c>
       <c r="O10" t="n">
-        <v>6.20695348090056</v>
+        <v>6.205149625824204</v>
       </c>
       <c r="P10" t="n">
-        <v>356.5834881273321</v>
+        <v>356.5505881615223</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -37458,7 +37556,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K736"/>
+  <dimension ref="A1:K738"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -79413,6 +79511,120 @@
         </is>
       </c>
     </row>
+    <row r="737">
+      <c r="A737" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-28 21:54:27+00:00</t>
+        </is>
+      </c>
+      <c r="B737" t="inlineStr">
+        <is>
+          <t>-40.021783719764386,176.89125908123157</t>
+        </is>
+      </c>
+      <c r="C737" t="inlineStr">
+        <is>
+          <t>-40.02243268015967,176.8909511768335</t>
+        </is>
+      </c>
+      <c r="D737" t="inlineStr">
+        <is>
+          <t>-40.02304128834358,176.89053099679404</t>
+        </is>
+      </c>
+      <c r="E737" t="inlineStr">
+        <is>
+          <t>-40.02365175779957,176.89011601161465</t>
+        </is>
+      </c>
+      <c r="F737" t="inlineStr">
+        <is>
+          <t>-40.02424011427568,176.88964340335949</t>
+        </is>
+      </c>
+      <c r="G737" t="inlineStr">
+        <is>
+          <t>-40.024826692109436,176.8891563523553</t>
+        </is>
+      </c>
+      <c r="H737" t="inlineStr">
+        <is>
+          <t>-40.02545916903367,176.8888039144847</t>
+        </is>
+      </c>
+      <c r="I737" t="inlineStr">
+        <is>
+          <t>-40.026088507600655,176.8884419473111</t>
+        </is>
+      </c>
+      <c r="J737" t="inlineStr">
+        <is>
+          <t>-40.0267267988091,176.88810745620736</t>
+        </is>
+      </c>
+      <c r="K737" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-15 22:00:37+00:00</t>
+        </is>
+      </c>
+      <c r="B738" t="inlineStr">
+        <is>
+          <t>-40.02178070995586,176.89125070564126</t>
+        </is>
+      </c>
+      <c r="C738" t="inlineStr">
+        <is>
+          <t>-40.022429898935236,176.890943437294</t>
+        </is>
+      </c>
+      <c r="D738" t="inlineStr">
+        <is>
+          <t>-40.02304033586371,176.89052834624576</t>
+        </is>
+      </c>
+      <c r="E738" t="inlineStr">
+        <is>
+          <t>-40.0236504243198,176.8901123008175</t>
+        </is>
+      </c>
+      <c r="F738" t="inlineStr">
+        <is>
+          <t>-40.02423893618316,176.88963998612803</t>
+        </is>
+      </c>
+      <c r="G738" t="inlineStr">
+        <is>
+          <t>-40.02482379535338,176.88914752611444</t>
+        </is>
+      </c>
+      <c r="H738" t="inlineStr">
+        <is>
+          <t>-40.02545526956777,176.88879195461504</t>
+        </is>
+      </c>
+      <c r="I738" t="inlineStr">
+        <is>
+          <t>-40.02608341367635,176.88842632392482</t>
+        </is>
+      </c>
+      <c r="J738" t="inlineStr">
+        <is>
+          <t>-40.02672335600341,176.88809689686022</t>
+        </is>
+      </c>
+      <c r="K738" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0304/nzd0304.xlsx
+++ b/data/nzd0304/nzd0304.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K738"/>
+  <dimension ref="A1:K741"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29226,6 +29226,123 @@
         <v>358.19</v>
       </c>
       <c r="K738" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-01 21:54:04+00:00</t>
+        </is>
+      </c>
+      <c r="B739" t="n">
+        <v>360.41</v>
+      </c>
+      <c r="C739" t="n">
+        <v>369.4</v>
+      </c>
+      <c r="D739" t="n">
+        <v>368.81</v>
+      </c>
+      <c r="E739" t="n">
+        <v>367.97</v>
+      </c>
+      <c r="F739" t="n">
+        <v>361.27</v>
+      </c>
+      <c r="G739" t="n">
+        <v>350.04</v>
+      </c>
+      <c r="H739" t="n">
+        <v>351.4</v>
+      </c>
+      <c r="I739" t="n">
+        <v>352.14</v>
+      </c>
+      <c r="J739" t="n">
+        <v>356.32</v>
+      </c>
+      <c r="K739" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-08 22:00:14+00:00</t>
+        </is>
+      </c>
+      <c r="B740" t="n">
+        <v>359.55</v>
+      </c>
+      <c r="C740" t="n">
+        <v>369.11</v>
+      </c>
+      <c r="D740" t="n">
+        <v>368.4</v>
+      </c>
+      <c r="E740" t="n">
+        <v>367.3</v>
+      </c>
+      <c r="F740" t="n">
+        <v>360.75</v>
+      </c>
+      <c r="G740" t="n">
+        <v>350.28</v>
+      </c>
+      <c r="H740" t="n">
+        <v>350.47</v>
+      </c>
+      <c r="I740" t="n">
+        <v>351.34</v>
+      </c>
+      <c r="J740" t="n">
+        <v>355.54</v>
+      </c>
+      <c r="K740" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-25 21:54:12+00:00</t>
+        </is>
+      </c>
+      <c r="B741" t="n">
+        <v>358.96</v>
+      </c>
+      <c r="C741" t="n">
+        <v>368.83</v>
+      </c>
+      <c r="D741" t="n">
+        <v>367.84</v>
+      </c>
+      <c r="E741" t="n">
+        <v>366.38</v>
+      </c>
+      <c r="F741" t="n">
+        <v>359.53</v>
+      </c>
+      <c r="G741" t="n">
+        <v>349.09</v>
+      </c>
+      <c r="H741" t="n">
+        <v>349.83</v>
+      </c>
+      <c r="I741" t="n">
+        <v>350.6</v>
+      </c>
+      <c r="J741" t="n">
+        <v>355.12</v>
+      </c>
+      <c r="K741" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -29242,7 +29359,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B746"/>
+  <dimension ref="A1:B749"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36705,6 +36822,36 @@
       </c>
       <c r="B746" t="n">
         <v>-0.47</v>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" t="inlineStr">
+        <is>
+          <t>2026-04-01 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B747" t="n">
+        <v>-0.39</v>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" t="inlineStr">
+        <is>
+          <t>2026-04-08 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B748" t="n">
+        <v>0.38</v>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" t="inlineStr">
+        <is>
+          <t>2026-04-25 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B749" t="n">
+        <v>-0.14</v>
       </c>
     </row>
   </sheetData>
@@ -36873,28 +37020,28 @@
         <v>0.0428</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.7325042989513069</v>
+        <v>-0.7307083058548997</v>
       </c>
       <c r="J2" t="n">
-        <v>737</v>
+        <v>740</v>
       </c>
       <c r="K2" t="n">
-        <v>737</v>
+        <v>740</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5301968171016744</v>
+        <v>0.5311800037680295</v>
       </c>
       <c r="M2" t="n">
-        <v>4.177763962536942</v>
+        <v>4.170523578282258</v>
       </c>
       <c r="N2" t="n">
-        <v>25.61101683925185</v>
+        <v>25.52664008863061</v>
       </c>
       <c r="O2" t="n">
-        <v>5.060732836186064</v>
+        <v>5.052389542447278</v>
       </c>
       <c r="P2" t="n">
-        <v>377.0603641920784</v>
+        <v>377.0413358437891</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -36951,28 +37098,28 @@
         <v>0.0458</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.6291267685657033</v>
+        <v>-0.6279003863002786</v>
       </c>
       <c r="J3" t="n">
-        <v>737</v>
+        <v>740</v>
       </c>
       <c r="K3" t="n">
-        <v>737</v>
+        <v>740</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4154174967140333</v>
+        <v>0.4167364280382395</v>
       </c>
       <c r="M3" t="n">
-        <v>4.355354194912446</v>
+        <v>4.344674208093227</v>
       </c>
       <c r="N3" t="n">
-        <v>30.00302088468148</v>
+        <v>29.89000905485691</v>
       </c>
       <c r="O3" t="n">
-        <v>5.477501335890433</v>
+        <v>5.467175601245757</v>
       </c>
       <c r="P3" t="n">
-        <v>384.4458057836142</v>
+        <v>384.4328107927607</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -37029,28 +37176,28 @@
         <v>0.0356</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.7958617393908172</v>
+        <v>-0.7924550518597785</v>
       </c>
       <c r="J4" t="n">
-        <v>737</v>
+        <v>740</v>
       </c>
       <c r="K4" t="n">
-        <v>737</v>
+        <v>740</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3923009382233861</v>
+        <v>0.3922518633674335</v>
       </c>
       <c r="M4" t="n">
-        <v>5.687489833903615</v>
+        <v>5.681267618950844</v>
       </c>
       <c r="N4" t="n">
-        <v>52.85329896270225</v>
+        <v>52.70466475414599</v>
       </c>
       <c r="O4" t="n">
-        <v>7.270027438923615</v>
+        <v>7.259797845267181</v>
       </c>
       <c r="P4" t="n">
-        <v>385.5517365995723</v>
+        <v>385.5156366215149</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -37107,28 +37254,28 @@
         <v>0.0368</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5622239839793493</v>
+        <v>-0.5563774527642805</v>
       </c>
       <c r="J5" t="n">
-        <v>737</v>
+        <v>740</v>
       </c>
       <c r="K5" t="n">
-        <v>737</v>
+        <v>740</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2750253480623746</v>
+        <v>0.2719255439455261</v>
       </c>
       <c r="M5" t="n">
-        <v>5.340910246332232</v>
+        <v>5.349496193198878</v>
       </c>
       <c r="N5" t="n">
-        <v>44.88450739533625</v>
+        <v>44.89582847026907</v>
       </c>
       <c r="O5" t="n">
-        <v>6.699590091590399</v>
+        <v>6.700434946350055</v>
       </c>
       <c r="P5" t="n">
-        <v>375.2926743097134</v>
+        <v>375.2307197434863</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -37185,28 +37332,28 @@
         <v>0.0361</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4226618347118999</v>
+        <v>-0.4156387587428043</v>
       </c>
       <c r="J6" t="n">
-        <v>737</v>
+        <v>740</v>
       </c>
       <c r="K6" t="n">
-        <v>737</v>
+        <v>740</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1855978102417259</v>
+        <v>0.1810325407236967</v>
       </c>
       <c r="M6" t="n">
-        <v>5.324439922851083</v>
+        <v>5.337614251045508</v>
       </c>
       <c r="N6" t="n">
-        <v>42.22598412391434</v>
+        <v>42.33340832190597</v>
       </c>
       <c r="O6" t="n">
-        <v>6.49815236231918</v>
+        <v>6.506412861316592</v>
       </c>
       <c r="P6" t="n">
-        <v>363.4786376525453</v>
+        <v>363.4042150774904</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -37263,28 +37410,28 @@
         <v>0.0362</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3256154313527374</v>
+        <v>-0.3201641745892621</v>
       </c>
       <c r="J7" t="n">
-        <v>737</v>
+        <v>740</v>
       </c>
       <c r="K7" t="n">
-        <v>737</v>
+        <v>740</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1105495305298865</v>
+        <v>0.1078452251261133</v>
       </c>
       <c r="M7" t="n">
-        <v>5.512498294997375</v>
+        <v>5.516831725403611</v>
       </c>
       <c r="N7" t="n">
-        <v>45.95179180393608</v>
+        <v>45.93311608750825</v>
       </c>
       <c r="O7" t="n">
-        <v>6.778775096131755</v>
+        <v>6.777397442050175</v>
       </c>
       <c r="P7" t="n">
-        <v>352.0385650989411</v>
+        <v>351.9807977766397</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -37341,28 +37488,28 @@
         <v>0.036</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2373694667079166</v>
+        <v>-0.2322539676451427</v>
       </c>
       <c r="J8" t="n">
-        <v>737</v>
+        <v>740</v>
       </c>
       <c r="K8" t="n">
-        <v>737</v>
+        <v>740</v>
       </c>
       <c r="L8" t="n">
-        <v>0.05620329222507847</v>
+        <v>0.05427916352035345</v>
       </c>
       <c r="M8" t="n">
-        <v>5.84689630976179</v>
+        <v>5.849007772308189</v>
       </c>
       <c r="N8" t="n">
-        <v>50.96758286268261</v>
+        <v>50.90931494581734</v>
       </c>
       <c r="O8" t="n">
-        <v>7.139158414174783</v>
+        <v>7.135076379816641</v>
       </c>
       <c r="P8" t="n">
-        <v>350.8451733032928</v>
+        <v>350.7909658179199</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -37419,28 +37566,28 @@
         <v>0.0354</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.207617935689081</v>
+        <v>-0.2040121532141395</v>
       </c>
       <c r="J9" t="n">
-        <v>737</v>
+        <v>740</v>
       </c>
       <c r="K9" t="n">
-        <v>737</v>
+        <v>740</v>
       </c>
       <c r="L9" t="n">
-        <v>0.04267890070838221</v>
+        <v>0.04159504217440779</v>
       </c>
       <c r="M9" t="n">
-        <v>5.898485603652763</v>
+        <v>5.892015105485854</v>
       </c>
       <c r="N9" t="n">
-        <v>52.08369306146195</v>
+        <v>51.94702967393659</v>
       </c>
       <c r="O9" t="n">
-        <v>7.216903287523115</v>
+        <v>7.207428783826906</v>
       </c>
       <c r="P9" t="n">
-        <v>352.6288542688844</v>
+        <v>352.590646611805</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -37497,28 +37644,28 @@
         <v>0.0406</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.124981995640974</v>
+        <v>-0.1229183922116423</v>
       </c>
       <c r="J10" t="n">
-        <v>737</v>
+        <v>740</v>
       </c>
       <c r="K10" t="n">
-        <v>737</v>
+        <v>740</v>
       </c>
       <c r="L10" t="n">
-        <v>0.02138599436122213</v>
+        <v>0.02088274849843319</v>
       </c>
       <c r="M10" t="n">
-        <v>4.951564505699505</v>
+        <v>4.941190869817451</v>
       </c>
       <c r="N10" t="n">
-        <v>38.50388187886627</v>
+        <v>38.37266343068764</v>
       </c>
       <c r="O10" t="n">
-        <v>6.205149625824204</v>
+        <v>6.1945672512846</v>
       </c>
       <c r="P10" t="n">
-        <v>356.5505881615223</v>
+        <v>356.5287228494113</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -37556,7 +37703,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K738"/>
+  <dimension ref="A1:K741"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -79625,6 +79772,177 @@
         </is>
       </c>
     </row>
+    <row r="739">
+      <c r="A739" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-01 21:54:04+00:00</t>
+        </is>
+      </c>
+      <c r="B739" t="inlineStr">
+        <is>
+          <t>-40.02177701436727,176.8912404216896</t>
+        </is>
+      </c>
+      <c r="C739" t="inlineStr">
+        <is>
+          <t>-40.022425631850105,176.89093156293322</t>
+        </is>
+      </c>
+      <c r="D739" t="inlineStr">
+        <is>
+          <t>-40.023037745118145,176.8905211367548</t>
+        </is>
+      </c>
+      <c r="E739" t="inlineStr">
+        <is>
+          <t>-40.02364890034275,176.89010805990665</t>
+        </is>
+      </c>
+      <c r="F739" t="inlineStr">
+        <is>
+          <t>-40.024236579997776,176.8896331516655</t>
+        </is>
+      </c>
+      <c r="G739" t="inlineStr">
+        <is>
+          <t>-40.02481930891271,176.88913385620623</t>
+        </is>
+      </c>
+      <c r="H739" t="inlineStr">
+        <is>
+          <t>-40.0254492622799,176.88877352995348</t>
+        </is>
+      </c>
+      <c r="I739" t="inlineStr">
+        <is>
+          <t>-40.026076984789384,176.88840660613698</t>
+        </is>
+      </c>
+      <c r="J739" t="inlineStr">
+        <is>
+          <t>-40.026716786565274,176.88807674790456</t>
+        </is>
+      </c>
+      <c r="K739" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-08 22:00:14+00:00</t>
+        </is>
+      </c>
+      <c r="B740" t="inlineStr">
+        <is>
+          <t>-40.02177373786525,176.8912313039601</t>
+        </is>
+      </c>
+      <c r="C740" t="inlineStr">
+        <is>
+          <t>-40.02242452697963,176.89092848832217</t>
+        </is>
+      </c>
+      <c r="D740" t="inlineStr">
+        <is>
+          <t>-40.023036183050756,176.8905167898561</t>
+        </is>
+      </c>
+      <c r="E740" t="inlineStr">
+        <is>
+          <t>-40.02364634768085,176.8901009563814</t>
+        </is>
+      </c>
+      <c r="F740" t="inlineStr">
+        <is>
+          <t>-40.024234665596836,176.88962759866502</t>
+        </is>
+      </c>
+      <c r="G740" t="inlineStr">
+        <is>
+          <t>-40.02482015674415,176.88913643949581</t>
+        </is>
+      </c>
+      <c r="H740" t="inlineStr">
+        <is>
+          <t>-40.02544599515712,176.88876350952478</t>
+        </is>
+      </c>
+      <c r="I740" t="inlineStr">
+        <is>
+          <t>-40.026074174345894,176.8883979863401</t>
+        </is>
+      </c>
+      <c r="J740" t="inlineStr">
+        <is>
+          <t>-40.026714046370735,176.88806834352843</t>
+        </is>
+      </c>
+      <c r="K740" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-25 21:54:12+00:00</t>
+        </is>
+      </c>
+      <c r="B741" t="inlineStr">
+        <is>
+          <t>-40.02177149003202,176.8912250487741</t>
+        </is>
+      </c>
+      <c r="C741" t="inlineStr">
+        <is>
+          <t>-40.02242346020806,176.8909255197323</t>
+        </is>
+      </c>
+      <c r="D741" t="inlineStr">
+        <is>
+          <t>-40.023034049495,176.89051085262892</t>
+        </is>
+      </c>
+      <c r="E741" t="inlineStr">
+        <is>
+          <t>-40.02364284253239,176.8900912022878</t>
+        </is>
+      </c>
+      <c r="F741" t="inlineStr">
+        <is>
+          <t>-40.02423017411664,176.88961457047273</t>
+        </is>
+      </c>
+      <c r="G741" t="inlineStr">
+        <is>
+          <t>-40.02481595291266,176.88912363068542</t>
+        </is>
+      </c>
+      <c r="H741" t="inlineStr">
+        <is>
+          <t>-40.025443746814034,176.88875661374647</t>
+        </is>
+      </c>
+      <c r="I741" t="inlineStr">
+        <is>
+          <t>-40.02607157468504,176.88839001302858</t>
+        </is>
+      </c>
+      <c r="J741" t="inlineStr">
+        <is>
+          <t>-40.026712570881095,176.8880638180954</t>
+        </is>
+      </c>
+      <c r="K741" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0304/nzd0304.xlsx
+++ b/data/nzd0304/nzd0304.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K741"/>
+  <dimension ref="A1:K747"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29343,6 +29343,240 @@
         <v>355.12</v>
       </c>
       <c r="K741" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02 22:00:18+00:00</t>
+        </is>
+      </c>
+      <c r="B742" t="n">
+        <v>358.95</v>
+      </c>
+      <c r="C742" t="n">
+        <v>368.77</v>
+      </c>
+      <c r="D742" t="n">
+        <v>367.42</v>
+      </c>
+      <c r="E742" t="n">
+        <v>365.63</v>
+      </c>
+      <c r="F742" t="n">
+        <v>358.35</v>
+      </c>
+      <c r="G742" t="n">
+        <v>348.33</v>
+      </c>
+      <c r="H742" t="n">
+        <v>349.44</v>
+      </c>
+      <c r="I742" t="n">
+        <v>350.53</v>
+      </c>
+      <c r="J742" t="n">
+        <v>354.93</v>
+      </c>
+      <c r="K742" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-03 21:53:52+00:00</t>
+        </is>
+      </c>
+      <c r="B743" t="n">
+        <v>359.2</v>
+      </c>
+      <c r="C743" t="n">
+        <v>368.96</v>
+      </c>
+      <c r="D743" t="n">
+        <v>367.55</v>
+      </c>
+      <c r="E743" t="n">
+        <v>365.23</v>
+      </c>
+      <c r="F743" t="n">
+        <v>357.6</v>
+      </c>
+      <c r="G743" t="n">
+        <v>347.93</v>
+      </c>
+      <c r="H743" t="n">
+        <v>348.9</v>
+      </c>
+      <c r="I743" t="n">
+        <v>350.63</v>
+      </c>
+      <c r="J743" t="n">
+        <v>354.95</v>
+      </c>
+      <c r="K743" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-11 21:53:59+00:00</t>
+        </is>
+      </c>
+      <c r="B744" t="n">
+        <v>357.54</v>
+      </c>
+      <c r="C744" t="n">
+        <v>367.9</v>
+      </c>
+      <c r="D744" t="n">
+        <v>365.5</v>
+      </c>
+      <c r="E744" t="n">
+        <v>364.45</v>
+      </c>
+      <c r="F744" t="n">
+        <v>357.47</v>
+      </c>
+      <c r="G744" t="n">
+        <v>347.4</v>
+      </c>
+      <c r="H744" t="n">
+        <v>347.66</v>
+      </c>
+      <c r="I744" t="n">
+        <v>348.93</v>
+      </c>
+      <c r="J744" t="n">
+        <v>353.99</v>
+      </c>
+      <c r="K744" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-18 22:00:01+00:00</t>
+        </is>
+      </c>
+      <c r="B745" t="n">
+        <v>356.87</v>
+      </c>
+      <c r="C745" t="n">
+        <v>367.35</v>
+      </c>
+      <c r="D745" t="n">
+        <v>365.06</v>
+      </c>
+      <c r="E745" t="n">
+        <v>363.38</v>
+      </c>
+      <c r="F745" t="n">
+        <v>356.71</v>
+      </c>
+      <c r="G745" t="n">
+        <v>346.32</v>
+      </c>
+      <c r="H745" t="n">
+        <v>345.63</v>
+      </c>
+      <c r="I745" t="n">
+        <v>347.59</v>
+      </c>
+      <c r="J745" t="n">
+        <v>352.79</v>
+      </c>
+      <c r="K745" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-19 21:53:34+00:00</t>
+        </is>
+      </c>
+      <c r="B746" t="n">
+        <v>356.95</v>
+      </c>
+      <c r="C746" t="n">
+        <v>367.64</v>
+      </c>
+      <c r="D746" t="n">
+        <v>365.3</v>
+      </c>
+      <c r="E746" t="n">
+        <v>363.45</v>
+      </c>
+      <c r="F746" t="n">
+        <v>356.41</v>
+      </c>
+      <c r="G746" t="n">
+        <v>345.89</v>
+      </c>
+      <c r="H746" t="n">
+        <v>345.68</v>
+      </c>
+      <c r="I746" t="n">
+        <v>347.43</v>
+      </c>
+      <c r="J746" t="n">
+        <v>352.92</v>
+      </c>
+      <c r="K746" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-27 21:53:46+00:00</t>
+        </is>
+      </c>
+      <c r="B747" t="n">
+        <v>356.34</v>
+      </c>
+      <c r="C747" t="n">
+        <v>367.13</v>
+      </c>
+      <c r="D747" t="n">
+        <v>364.92</v>
+      </c>
+      <c r="E747" t="n">
+        <v>362.86</v>
+      </c>
+      <c r="F747" t="n">
+        <v>355.18</v>
+      </c>
+      <c r="G747" t="n">
+        <v>344.61</v>
+      </c>
+      <c r="H747" t="n">
+        <v>344.16</v>
+      </c>
+      <c r="I747" t="n">
+        <v>346.03</v>
+      </c>
+      <c r="J747" t="n">
+        <v>352.27</v>
+      </c>
+      <c r="K747" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -29359,7 +29593,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B749"/>
+  <dimension ref="A1:B755"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36852,6 +37086,66 @@
       </c>
       <c r="B749" t="n">
         <v>-0.14</v>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" t="inlineStr">
+        <is>
+          <t>2026-05-02 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B750" t="n">
+        <v>-0.16</v>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" t="inlineStr">
+        <is>
+          <t>2026-05-03 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B751" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" t="inlineStr">
+        <is>
+          <t>2026-05-11 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B752" t="n">
+        <v>-0.13</v>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" t="inlineStr">
+        <is>
+          <t>2026-05-18 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B753" t="n">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" t="inlineStr">
+        <is>
+          <t>2026-05-19 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B754" t="n">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" t="inlineStr">
+        <is>
+          <t>2026-05-27 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B755" t="n">
+        <v>-0.55</v>
       </c>
     </row>
   </sheetData>
@@ -37020,28 +37314,28 @@
         <v>0.0428</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.7307083058548997</v>
+        <v>-0.730445577309953</v>
       </c>
       <c r="J2" t="n">
-        <v>740</v>
+        <v>746</v>
       </c>
       <c r="K2" t="n">
-        <v>740</v>
+        <v>746</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5311800037680295</v>
+        <v>0.5356466160799058</v>
       </c>
       <c r="M2" t="n">
-        <v>4.170523578282258</v>
+        <v>4.144424606812129</v>
       </c>
       <c r="N2" t="n">
-        <v>25.52664008863061</v>
+        <v>25.3305174516054</v>
       </c>
       <c r="O2" t="n">
-        <v>5.052389542447278</v>
+        <v>5.032943219588851</v>
       </c>
       <c r="P2" t="n">
-        <v>377.0413358437891</v>
+        <v>377.0385596792391</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -37098,28 +37392,28 @@
         <v>0.0458</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.6279003863002786</v>
+        <v>-0.6273461949919248</v>
       </c>
       <c r="J3" t="n">
-        <v>740</v>
+        <v>746</v>
       </c>
       <c r="K3" t="n">
-        <v>740</v>
+        <v>746</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4167364280382395</v>
+        <v>0.4209013049951255</v>
       </c>
       <c r="M3" t="n">
-        <v>4.344674208093227</v>
+        <v>4.314873423257895</v>
       </c>
       <c r="N3" t="n">
-        <v>29.89000905485691</v>
+        <v>29.65411280056289</v>
       </c>
       <c r="O3" t="n">
-        <v>5.467175601245757</v>
+        <v>5.445558997987524</v>
       </c>
       <c r="P3" t="n">
-        <v>384.4328107927607</v>
+        <v>384.4269282947016</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -37176,28 +37470,28 @@
         <v>0.0356</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.7924550518597785</v>
+        <v>-0.7897086031291566</v>
       </c>
       <c r="J4" t="n">
-        <v>740</v>
+        <v>746</v>
       </c>
       <c r="K4" t="n">
-        <v>740</v>
+        <v>746</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3922518633674335</v>
+        <v>0.3949952743621374</v>
       </c>
       <c r="M4" t="n">
-        <v>5.681267618950844</v>
+        <v>5.648941864955278</v>
       </c>
       <c r="N4" t="n">
-        <v>52.70466475414599</v>
+        <v>52.31168272857187</v>
       </c>
       <c r="O4" t="n">
-        <v>7.259797845267181</v>
+        <v>7.232681572457885</v>
       </c>
       <c r="P4" t="n">
-        <v>385.5156366215149</v>
+        <v>385.4864458518978</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -37254,28 +37548,28 @@
         <v>0.0368</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5563774527642805</v>
+        <v>-0.5500340799714674</v>
       </c>
       <c r="J5" t="n">
-        <v>740</v>
+        <v>746</v>
       </c>
       <c r="K5" t="n">
-        <v>740</v>
+        <v>746</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2719255439455261</v>
+        <v>0.2706087342019535</v>
       </c>
       <c r="M5" t="n">
-        <v>5.349496193198878</v>
+        <v>5.339299603815644</v>
       </c>
       <c r="N5" t="n">
-        <v>44.89582847026907</v>
+        <v>44.6576670682856</v>
       </c>
       <c r="O5" t="n">
-        <v>6.700434946350055</v>
+        <v>6.682639229248097</v>
       </c>
       <c r="P5" t="n">
-        <v>375.2307197434863</v>
+        <v>375.1632762654118</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -37332,28 +37626,28 @@
         <v>0.0361</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4156387587428043</v>
+        <v>-0.4078976869734622</v>
       </c>
       <c r="J6" t="n">
-        <v>740</v>
+        <v>746</v>
       </c>
       <c r="K6" t="n">
-        <v>740</v>
+        <v>746</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1810325407236967</v>
+        <v>0.1776729207247237</v>
       </c>
       <c r="M6" t="n">
-        <v>5.337614251045508</v>
+        <v>5.333361487004377</v>
       </c>
       <c r="N6" t="n">
-        <v>42.33340832190597</v>
+        <v>42.17197303569122</v>
       </c>
       <c r="O6" t="n">
-        <v>6.506412861316592</v>
+        <v>6.493995152114854</v>
       </c>
       <c r="P6" t="n">
-        <v>363.4042150774904</v>
+        <v>363.3219068074506</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -37410,28 +37704,28 @@
         <v>0.0362</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3201641745892621</v>
+        <v>-0.3146379393285262</v>
       </c>
       <c r="J7" t="n">
-        <v>740</v>
+        <v>746</v>
       </c>
       <c r="K7" t="n">
-        <v>740</v>
+        <v>746</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1078452251261133</v>
+        <v>0.1061264318553155</v>
       </c>
       <c r="M7" t="n">
-        <v>5.516831725403611</v>
+        <v>5.499214754764563</v>
       </c>
       <c r="N7" t="n">
-        <v>45.93311608750825</v>
+        <v>45.66387845930898</v>
       </c>
       <c r="O7" t="n">
-        <v>6.777397442050175</v>
+        <v>6.757505342899033</v>
       </c>
       <c r="P7" t="n">
-        <v>351.9807977766397</v>
+        <v>351.922049041026</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -37488,28 +37782,28 @@
         <v>0.036</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2322539676451427</v>
+        <v>-0.228383848351588</v>
       </c>
       <c r="J8" t="n">
-        <v>740</v>
+        <v>746</v>
       </c>
       <c r="K8" t="n">
-        <v>740</v>
+        <v>746</v>
       </c>
       <c r="L8" t="n">
-        <v>0.05427916352035345</v>
+        <v>0.05346381580650239</v>
       </c>
       <c r="M8" t="n">
-        <v>5.849007772308189</v>
+        <v>5.822551809919124</v>
       </c>
       <c r="N8" t="n">
-        <v>50.90931494581734</v>
+        <v>50.57153396730972</v>
       </c>
       <c r="O8" t="n">
-        <v>7.135076379816641</v>
+        <v>7.111366533044807</v>
       </c>
       <c r="P8" t="n">
-        <v>350.7909658179199</v>
+        <v>350.74984063135</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -37566,28 +37860,28 @@
         <v>0.0354</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2040121532141395</v>
+        <v>-0.2017118647142641</v>
       </c>
       <c r="J9" t="n">
-        <v>740</v>
+        <v>746</v>
       </c>
       <c r="K9" t="n">
-        <v>740</v>
+        <v>746</v>
       </c>
       <c r="L9" t="n">
-        <v>0.04159504217440779</v>
+        <v>0.04142073169614924</v>
       </c>
       <c r="M9" t="n">
-        <v>5.892015105485854</v>
+        <v>5.858647102085438</v>
       </c>
       <c r="N9" t="n">
-        <v>51.94702967393659</v>
+        <v>51.56692549419357</v>
       </c>
       <c r="O9" t="n">
-        <v>7.207428783826906</v>
+        <v>7.181011453423088</v>
       </c>
       <c r="P9" t="n">
-        <v>352.590646611805</v>
+        <v>352.5662126273793</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -37644,28 +37938,28 @@
         <v>0.0406</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1229183922116423</v>
+        <v>-0.1222530617577204</v>
       </c>
       <c r="J10" t="n">
-        <v>740</v>
+        <v>746</v>
       </c>
       <c r="K10" t="n">
-        <v>740</v>
+        <v>746</v>
       </c>
       <c r="L10" t="n">
-        <v>0.02088274849843319</v>
+        <v>0.02104505911753707</v>
       </c>
       <c r="M10" t="n">
-        <v>4.941190869817451</v>
+        <v>4.909259155435438</v>
       </c>
       <c r="N10" t="n">
-        <v>38.37266343068764</v>
+        <v>38.07414210911168</v>
       </c>
       <c r="O10" t="n">
-        <v>6.1945672512846</v>
+        <v>6.170424791625912</v>
       </c>
       <c r="P10" t="n">
-        <v>356.5287228494113</v>
+        <v>356.5216652513038</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -37703,7 +37997,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K741"/>
+  <dimension ref="A1:K747"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -79943,6 +80237,348 @@
         </is>
       </c>
     </row>
+    <row r="742">
+      <c r="A742" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02 22:00:18+00:00</t>
+        </is>
+      </c>
+      <c r="B742" t="inlineStr">
+        <is>
+          <t>-40.02177145193315,176.89122494275398</t>
+        </is>
+      </c>
+      <c r="C742" t="inlineStr">
+        <is>
+          <t>-40.02242323161413,176.8909248836059</t>
+        </is>
+      </c>
+      <c r="D742" t="inlineStr">
+        <is>
+          <t>-40.023032449327964,176.89050639970873</t>
+        </is>
+      </c>
+      <c r="E742" t="inlineStr">
+        <is>
+          <t>-40.023639985073764,176.8900832505818</t>
+        </is>
+      </c>
+      <c r="F742" t="inlineStr">
+        <is>
+          <t>-40.02422582989657,176.88960196943583</t>
+        </is>
+      </c>
+      <c r="G742" t="inlineStr">
+        <is>
+          <t>-40.02481326811194,176.8891154502695</t>
+        </is>
+      </c>
+      <c r="H742" t="inlineStr">
+        <is>
+          <t>-40.02544237672976,176.88875241163174</t>
+        </is>
+      </c>
+      <c r="I742" t="inlineStr">
+        <is>
+          <t>-40.02607132877117,176.88838925879645</t>
+        </is>
+      </c>
+      <c r="J742" t="inlineStr">
+        <is>
+          <t>-40.02671190339762,176.88806177087577</t>
+        </is>
+      </c>
+      <c r="K742" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-03 21:53:52+00:00</t>
+        </is>
+      </c>
+      <c r="B743" t="inlineStr">
+        <is>
+          <t>-40.021772404404906,176.89122759325647</t>
+        </is>
+      </c>
+      <c r="C743" t="inlineStr">
+        <is>
+          <t>-40.022423955494865,176.89092689800617</t>
+        </is>
+      </c>
+      <c r="D743" t="inlineStr">
+        <is>
+          <t>-40.02303294461777,176.89050777799352</t>
+        </is>
+      </c>
+      <c r="E743" t="inlineStr">
+        <is>
+          <t>-40.02363846109559,176.89007900967218</t>
+        </is>
+      </c>
+      <c r="F743" t="inlineStr">
+        <is>
+          <t>-40.02422306873902,176.889593960303</t>
+        </is>
+      </c>
+      <c r="G743" t="inlineStr">
+        <is>
+          <t>-40.02481185505869,176.88911114478765</t>
+        </is>
+      </c>
+      <c r="H743" t="inlineStr">
+        <is>
+          <t>-40.02544047968972,176.8887465933193</t>
+        </is>
+      </c>
+      <c r="I743" t="inlineStr">
+        <is>
+          <t>-40.02607168007672,176.88839033627096</t>
+        </is>
+      </c>
+      <c r="J743" t="inlineStr">
+        <is>
+          <t>-40.02671197365905,176.88806198637255</t>
+        </is>
+      </c>
+      <c r="K743" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-11 21:53:59+00:00</t>
+        </is>
+      </c>
+      <c r="B744" t="inlineStr">
+        <is>
+          <t>-40.021766079991274,176.8912099939212</t>
+        </is>
+      </c>
+      <c r="C744" t="inlineStr">
+        <is>
+          <t>-40.02241991700191,176.89091565977364</t>
+        </is>
+      </c>
+      <c r="D744" t="inlineStr">
+        <is>
+          <t>-40.02302513427636,176.89048604350478</t>
+        </is>
+      </c>
+      <c r="E744" t="inlineStr">
+        <is>
+          <t>-40.023635489337664,176.89007073989893</t>
+        </is>
+      </c>
+      <c r="F744" t="inlineStr">
+        <is>
+          <t>-40.02422259013831,176.88959257205335</t>
+        </is>
+      </c>
+      <c r="G744" t="inlineStr">
+        <is>
+          <t>-40.02480998276287,176.88910544002445</t>
+        </is>
+      </c>
+      <c r="H744" t="inlineStr">
+        <is>
+          <t>-40.02543612352254,176.88873323275112</t>
+        </is>
+      </c>
+      <c r="I744" t="inlineStr">
+        <is>
+          <t>-40.02606570788074,176.88837201920606</t>
+        </is>
+      </c>
+      <c r="J744" t="inlineStr">
+        <is>
+          <t>-40.026708601110435,176.88805164252648</t>
+        </is>
+      </c>
+      <c r="K744" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-18 22:00:01+00:00</t>
+        </is>
+      </c>
+      <c r="B745" t="inlineStr">
+        <is>
+          <t>-40.021763527365685,176.89120289057587</t>
+        </is>
+      </c>
+      <c r="C745" t="inlineStr">
+        <is>
+          <t>-40.02241782155699,176.89090982861578</t>
+        </is>
+      </c>
+      <c r="D745" t="inlineStr">
+        <is>
+          <t>-40.02302345790983,176.89048137854198</t>
+        </is>
+      </c>
+      <c r="E745" t="inlineStr">
+        <is>
+          <t>-40.02363141269439,176.89005939546752</t>
+        </is>
+      </c>
+      <c r="F745" t="inlineStr">
+        <is>
+          <t>-40.02421979216461,176.8895844561328</t>
+        </is>
+      </c>
+      <c r="G745" t="inlineStr">
+        <is>
+          <t>-40.02480616751762,176.88909381522492</t>
+        </is>
+      </c>
+      <c r="H745" t="inlineStr">
+        <is>
+          <t>-40.025428992051786,176.88871136021157</t>
+        </is>
+      </c>
+      <c r="I745" t="inlineStr">
+        <is>
+          <t>-40.026061000382946,176.88835758105117</t>
+        </is>
+      </c>
+      <c r="J745" t="inlineStr">
+        <is>
+          <t>-40.026704385423294,176.88803871272017</t>
+        </is>
+      </c>
+      <c r="K745" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-19 21:53:34+00:00</t>
+        </is>
+      </c>
+      <c r="B746" t="inlineStr">
+        <is>
+          <t>-40.02176383215682,176.8912037387365</t>
+        </is>
+      </c>
+      <c r="C746" t="inlineStr">
+        <is>
+          <t>-40.02241892642799,176.89091290322628</t>
+        </is>
+      </c>
+      <c r="D746" t="inlineStr">
+        <is>
+          <t>-40.0230243722916,176.8904839230671</t>
+        </is>
+      </c>
+      <c r="E746" t="inlineStr">
+        <is>
+          <t>-40.02363167939072,176.89006013762653</t>
+        </is>
+      </c>
+      <c r="F746" t="inlineStr">
+        <is>
+          <t>-40.02421868770114,176.88958125248013</t>
+        </is>
+      </c>
+      <c r="G746" t="inlineStr">
+        <is>
+          <t>-40.02480464848445,176.88908918683288</t>
+        </is>
+      </c>
+      <c r="H746" t="inlineStr">
+        <is>
+          <t>-40.02542916770381,176.88871189894402</t>
+        </is>
+      </c>
+      <c r="I746" t="inlineStr">
+        <is>
+          <t>-40.02606043829353,176.88835585709248</t>
+        </is>
+      </c>
+      <c r="J746" t="inlineStr">
+        <is>
+          <t>-40.02670484212282,176.88804011344914</t>
+        </is>
+      </c>
+      <c r="K746" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-27 21:53:46+00:00</t>
+        </is>
+      </c>
+      <c r="B747" t="inlineStr">
+        <is>
+          <t>-40.021761508124214,176.89119727151206</t>
+        </is>
+      </c>
+      <c r="C747" t="inlineStr">
+        <is>
+          <t>-40.02241698337894,176.89090749615272</t>
+        </is>
+      </c>
+      <c r="D747" t="inlineStr">
+        <is>
+          <t>-40.02302292452043,176.89047989423565</t>
+        </is>
+      </c>
+      <c r="E747" t="inlineStr">
+        <is>
+          <t>-40.02362943152153,176.89005388228637</t>
+        </is>
+      </c>
+      <c r="F747" t="inlineStr">
+        <is>
+          <t>-40.02421415939993,176.8895681175052</t>
+        </is>
+      </c>
+      <c r="G747" t="inlineStr">
+        <is>
+          <t>-40.02480012671013,176.88907540929486</t>
+        </is>
+      </c>
+      <c r="H747" t="inlineStr">
+        <is>
+          <t>-40.02542382788059,176.8886955214787</t>
+        </is>
+      </c>
+      <c r="I747" t="inlineStr">
+        <is>
+          <t>-40.026055520009976,176.88834077245528</t>
+        </is>
+      </c>
+      <c r="J747" t="inlineStr">
+        <is>
+          <t>-40.02670255862506,176.8880331098046</t>
+        </is>
+      </c>
+      <c r="K747" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0304/nzd0304.xlsx
+++ b/data/nzd0304/nzd0304.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K747"/>
+  <dimension ref="A1:K750"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29577,6 +29577,123 @@
         <v>352.27</v>
       </c>
       <c r="K747" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-03 21:59:53+00:00</t>
+        </is>
+      </c>
+      <c r="B748" t="n">
+        <v>355.77</v>
+      </c>
+      <c r="C748" t="n">
+        <v>367.3</v>
+      </c>
+      <c r="D748" t="n">
+        <v>364.75</v>
+      </c>
+      <c r="E748" t="n">
+        <v>361.98</v>
+      </c>
+      <c r="F748" t="n">
+        <v>353.31</v>
+      </c>
+      <c r="G748" t="n">
+        <v>343.16</v>
+      </c>
+      <c r="H748" t="n">
+        <v>343.35</v>
+      </c>
+      <c r="I748" t="n">
+        <v>344.65</v>
+      </c>
+      <c r="J748" t="n">
+        <v>351.66</v>
+      </c>
+      <c r="K748" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-11 21:59:45+00:00</t>
+        </is>
+      </c>
+      <c r="B749" t="n">
+        <v>355.65</v>
+      </c>
+      <c r="C749" t="n">
+        <v>367.07</v>
+      </c>
+      <c r="D749" t="n">
+        <v>364.3</v>
+      </c>
+      <c r="E749" t="n">
+        <v>361.41</v>
+      </c>
+      <c r="F749" t="n">
+        <v>351.71</v>
+      </c>
+      <c r="G749" t="n">
+        <v>342.1</v>
+      </c>
+      <c r="H749" t="n">
+        <v>342.65</v>
+      </c>
+      <c r="I749" t="n">
+        <v>343.97</v>
+      </c>
+      <c r="J749" t="n">
+        <v>350.88</v>
+      </c>
+      <c r="K749" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-12 21:53:46+00:00</t>
+        </is>
+      </c>
+      <c r="B750" t="n">
+        <v>356.01</v>
+      </c>
+      <c r="C750" t="n">
+        <v>367.56</v>
+      </c>
+      <c r="D750" t="n">
+        <v>364.62</v>
+      </c>
+      <c r="E750" t="n">
+        <v>361.45</v>
+      </c>
+      <c r="F750" t="n">
+        <v>351.02</v>
+      </c>
+      <c r="G750" t="n">
+        <v>341.69</v>
+      </c>
+      <c r="H750" t="n">
+        <v>342.39</v>
+      </c>
+      <c r="I750" t="n">
+        <v>344.18</v>
+      </c>
+      <c r="J750" t="n">
+        <v>350.87</v>
+      </c>
+      <c r="K750" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -29593,7 +29710,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B755"/>
+  <dimension ref="A1:B758"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37146,6 +37263,36 @@
       </c>
       <c r="B755" t="n">
         <v>-0.55</v>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" t="inlineStr">
+        <is>
+          <t>2026-06-03 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B756" t="n">
+        <v>0.24</v>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" t="inlineStr">
+        <is>
+          <t>2026-06-11 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B757" t="n">
+        <v>-0.43</v>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" t="inlineStr">
+        <is>
+          <t>2026-06-12 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B758" t="n">
+        <v>-0.6899999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -37314,28 +37461,28 @@
         <v>0.0428</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.730445577309953</v>
+        <v>-0.7317774661471096</v>
       </c>
       <c r="J2" t="n">
-        <v>746</v>
+        <v>749</v>
       </c>
       <c r="K2" t="n">
-        <v>746</v>
+        <v>749</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5356466160799058</v>
+        <v>0.5387830194823473</v>
       </c>
       <c r="M2" t="n">
-        <v>4.144424606812129</v>
+        <v>4.133445155332894</v>
       </c>
       <c r="N2" t="n">
-        <v>25.3305174516054</v>
+        <v>25.23951204049981</v>
       </c>
       <c r="O2" t="n">
-        <v>5.032943219588851</v>
+        <v>5.023894111195002</v>
       </c>
       <c r="P2" t="n">
-        <v>377.0385596792391</v>
+        <v>377.0527649445525</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -37392,28 +37539,28 @@
         <v>0.0458</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.6273461949919248</v>
+        <v>-0.6275741842152786</v>
       </c>
       <c r="J3" t="n">
-        <v>746</v>
+        <v>749</v>
       </c>
       <c r="K3" t="n">
-        <v>746</v>
+        <v>749</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4209013049951255</v>
+        <v>0.423364386617116</v>
       </c>
       <c r="M3" t="n">
-        <v>4.314873423257895</v>
+        <v>4.29849483788151</v>
       </c>
       <c r="N3" t="n">
-        <v>29.65411280056289</v>
+        <v>29.53580290231836</v>
       </c>
       <c r="O3" t="n">
-        <v>5.445558997987524</v>
+        <v>5.434685170487649</v>
       </c>
       <c r="P3" t="n">
-        <v>384.4269282947016</v>
+        <v>384.4293598218932</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -37470,28 +37617,28 @@
         <v>0.0356</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.7897086031291566</v>
+        <v>-0.7894870234394959</v>
       </c>
       <c r="J4" t="n">
-        <v>746</v>
+        <v>749</v>
       </c>
       <c r="K4" t="n">
-        <v>746</v>
+        <v>749</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3949952743621374</v>
+        <v>0.3971042315989464</v>
       </c>
       <c r="M4" t="n">
-        <v>5.648941864955278</v>
+        <v>5.627381670257527</v>
       </c>
       <c r="N4" t="n">
-        <v>52.31168272857187</v>
+        <v>52.1025782776925</v>
       </c>
       <c r="O4" t="n">
-        <v>7.232681572457885</v>
+        <v>7.218211570582598</v>
       </c>
       <c r="P4" t="n">
-        <v>385.4864458518978</v>
+        <v>385.4840829980301</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -37548,28 +37695,28 @@
         <v>0.0368</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5500340799714674</v>
+        <v>-0.5490356800943019</v>
       </c>
       <c r="J5" t="n">
-        <v>746</v>
+        <v>749</v>
       </c>
       <c r="K5" t="n">
-        <v>746</v>
+        <v>749</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2706087342019535</v>
+        <v>0.2717186196505713</v>
       </c>
       <c r="M5" t="n">
-        <v>5.339299603815644</v>
+        <v>5.32303252982173</v>
       </c>
       <c r="N5" t="n">
-        <v>44.6576670682856</v>
+        <v>44.48488237838446</v>
       </c>
       <c r="O5" t="n">
-        <v>6.682639229248097</v>
+        <v>6.669698822164646</v>
       </c>
       <c r="P5" t="n">
-        <v>375.1632762654118</v>
+        <v>375.1526286604281</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -37626,28 +37773,28 @@
         <v>0.0361</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4078976869734622</v>
+        <v>-0.408193250837105</v>
       </c>
       <c r="J6" t="n">
-        <v>746</v>
+        <v>749</v>
       </c>
       <c r="K6" t="n">
-        <v>746</v>
+        <v>749</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1776729207247237</v>
+        <v>0.1792469675480244</v>
       </c>
       <c r="M6" t="n">
-        <v>5.333361487004377</v>
+        <v>5.315856259231758</v>
       </c>
       <c r="N6" t="n">
-        <v>42.17197303569122</v>
+        <v>42.00720829987559</v>
       </c>
       <c r="O6" t="n">
-        <v>6.493995152114854</v>
+        <v>6.481296806957354</v>
       </c>
       <c r="P6" t="n">
-        <v>363.3219068074506</v>
+        <v>363.3250628389482</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -37704,28 +37851,28 @@
         <v>0.0362</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3146379393285262</v>
+        <v>-0.3155918177682969</v>
       </c>
       <c r="J7" t="n">
-        <v>746</v>
+        <v>749</v>
       </c>
       <c r="K7" t="n">
-        <v>746</v>
+        <v>749</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1061264318553155</v>
+        <v>0.1075856827744305</v>
       </c>
       <c r="M7" t="n">
-        <v>5.499214754764563</v>
+        <v>5.481779975435365</v>
       </c>
       <c r="N7" t="n">
-        <v>45.66387845930898</v>
+        <v>45.48780918747049</v>
       </c>
       <c r="O7" t="n">
-        <v>6.757505342899033</v>
+        <v>6.744465077933942</v>
       </c>
       <c r="P7" t="n">
-        <v>351.922049041026</v>
+        <v>351.932225154236</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -37782,28 +37929,28 @@
         <v>0.036</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.228383848351588</v>
+        <v>-0.2298820909560887</v>
       </c>
       <c r="J8" t="n">
-        <v>746</v>
+        <v>749</v>
       </c>
       <c r="K8" t="n">
-        <v>746</v>
+        <v>749</v>
       </c>
       <c r="L8" t="n">
-        <v>0.05346381580650239</v>
+        <v>0.05459798532458338</v>
       </c>
       <c r="M8" t="n">
-        <v>5.822551809919124</v>
+        <v>5.806140117373826</v>
       </c>
       <c r="N8" t="n">
-        <v>50.57153396730972</v>
+        <v>50.38272876032064</v>
       </c>
       <c r="O8" t="n">
-        <v>7.111366533044807</v>
+        <v>7.098079230349619</v>
       </c>
       <c r="P8" t="n">
-        <v>350.74984063135</v>
+        <v>350.7658219243725</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -37860,28 +38007,28 @@
         <v>0.0354</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2017118647142641</v>
+        <v>-0.204084050509701</v>
       </c>
       <c r="J9" t="n">
-        <v>746</v>
+        <v>749</v>
       </c>
       <c r="K9" t="n">
-        <v>746</v>
+        <v>749</v>
       </c>
       <c r="L9" t="n">
-        <v>0.04142073169614924</v>
+        <v>0.04271517716072915</v>
       </c>
       <c r="M9" t="n">
-        <v>5.858647102085438</v>
+        <v>5.84668561780264</v>
       </c>
       <c r="N9" t="n">
-        <v>51.56692549419357</v>
+        <v>51.3935472219848</v>
       </c>
       <c r="O9" t="n">
-        <v>7.181011453423088</v>
+        <v>7.168929293973041</v>
       </c>
       <c r="P9" t="n">
-        <v>352.5662126273793</v>
+        <v>352.5915145515539</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -37938,28 +38085,28 @@
         <v>0.0406</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1222530617577204</v>
+        <v>-0.1239846539155291</v>
       </c>
       <c r="J10" t="n">
-        <v>746</v>
+        <v>749</v>
       </c>
       <c r="K10" t="n">
-        <v>746</v>
+        <v>749</v>
       </c>
       <c r="L10" t="n">
-        <v>0.02104505911753707</v>
+        <v>0.02182184838796319</v>
       </c>
       <c r="M10" t="n">
-        <v>4.909259155435438</v>
+        <v>4.898074987916017</v>
       </c>
       <c r="N10" t="n">
-        <v>38.07414210911168</v>
+        <v>37.939691430906</v>
       </c>
       <c r="O10" t="n">
-        <v>6.170424791625912</v>
+        <v>6.159520389681813</v>
       </c>
       <c r="P10" t="n">
-        <v>356.5216652513038</v>
+        <v>356.5401352586745</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -37997,7 +38144,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K747"/>
+  <dimension ref="A1:K750"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -80579,6 +80726,177 @@
         </is>
       </c>
     </row>
+    <row r="748">
+      <c r="A748" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-03 21:59:53+00:00</t>
+        </is>
+      </c>
+      <c r="B748" t="inlineStr">
+        <is>
+          <t>-40.021759336486845,176.89119122836826</t>
+        </is>
+      </c>
+      <c r="C748" t="inlineStr">
+        <is>
+          <t>-40.022417631061984,176.89090929851054</t>
+        </is>
+      </c>
+      <c r="D748" t="inlineStr">
+        <is>
+          <t>-40.023022276833295,176.89047809186374</t>
+        </is>
+      </c>
+      <c r="E748" t="inlineStr">
+        <is>
+          <t>-40.023626078766824,176.89004455228817</t>
+        </is>
+      </c>
+      <c r="F748" t="inlineStr">
+        <is>
+          <t>-40.02420727490645,176.8895481480749</t>
+        </is>
+      </c>
+      <c r="G748" t="inlineStr">
+        <is>
+          <t>-40.024795004385574,176.88905980192965</t>
+        </is>
+      </c>
+      <c r="H748" t="inlineStr">
+        <is>
+          <t>-40.02542098231587,176.88868679401463</t>
+        </is>
+      </c>
+      <c r="I748" t="inlineStr">
+        <is>
+          <t>-40.0260506719856,176.8883259033149</t>
+        </is>
+      </c>
+      <c r="J748" t="inlineStr">
+        <is>
+          <t>-40.02670041564985,176.888026537154</t>
+        </is>
+      </c>
+      <c r="K748" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-11 21:59:45+00:00</t>
+        </is>
+      </c>
+      <c r="B749" t="inlineStr">
+        <is>
+          <t>-40.021758879299995,176.89118995612753</t>
+        </is>
+      </c>
+      <c r="C749" t="inlineStr">
+        <is>
+          <t>-40.02241675478491,176.89090686002646</t>
+        </is>
+      </c>
+      <c r="D749" t="inlineStr">
+        <is>
+          <t>-40.023020562367165,176.8904733208794</t>
+        </is>
+      </c>
+      <c r="E749" t="inlineStr">
+        <is>
+          <t>-40.02362390709573,176.89003850899437</t>
+        </is>
+      </c>
+      <c r="F749" t="inlineStr">
+        <is>
+          <t>-40.02420138442786,176.88953106193435</t>
+        </is>
+      </c>
+      <c r="G749" t="inlineStr">
+        <is>
+          <t>-40.02479125978829,176.88904839240885</t>
+        </is>
+      </c>
+      <c r="H749" t="inlineStr">
+        <is>
+          <t>-40.02541852318532,176.88867925176226</t>
+        </is>
+      </c>
+      <c r="I749" t="inlineStr">
+        <is>
+          <t>-40.026048283103265,176.88831857649282</t>
+        </is>
+      </c>
+      <c r="J749" t="inlineStr">
+        <is>
+          <t>-40.026697675451445,176.88801813278164</t>
+        </is>
+      </c>
+      <c r="K749" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-12 21:53:46+00:00</t>
+        </is>
+      </c>
+      <c r="B750" t="inlineStr">
+        <is>
+          <t>-40.02176025086051,176.89119377284982</t>
+        </is>
+      </c>
+      <c r="C750" t="inlineStr">
+        <is>
+          <t>-40.022418621635985,176.89091205505784</t>
+        </is>
+      </c>
+      <c r="D750" t="inlineStr">
+        <is>
+          <t>-40.0230217815431,176.89047671357935</t>
+        </is>
+      </c>
+      <c r="E750" t="inlineStr">
+        <is>
+          <t>-40.02362405949371,176.89003893308515</t>
+        </is>
+      </c>
+      <c r="F750" t="inlineStr">
+        <is>
+          <t>-40.02419884415814,176.88952369353711</t>
+        </is>
+      </c>
+      <c r="G750" t="inlineStr">
+        <is>
+          <t>-40.024789811406,176.88904397929267</t>
+        </is>
+      </c>
+      <c r="H750" t="inlineStr">
+        <is>
+          <t>-40.02541760979384,176.88867645035435</t>
+        </is>
+      </c>
+      <c r="I750" t="inlineStr">
+        <is>
+          <t>-40.02604902084639,176.88832083918783</t>
+        </is>
+      </c>
+      <c r="J750" t="inlineStr">
+        <is>
+          <t>-40.026697640320705,176.8880180250333</t>
+        </is>
+      </c>
+      <c r="K750" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
